--- a/api/_modelo_report.xlsx
+++ b/api/_modelo_report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego.batista\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego.batista\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C774446-84B2-4753-AB52-5C4FFD3205C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D2B288-5818-40DF-9E66-9D9C5AC8ABDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" xr2:uid="{A61D48FF-59C3-42AE-88A3-50A1935DB5F5}"/>
   </bookViews>
@@ -1970,17 +1970,494 @@
     <xf numFmtId="14" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="38" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="9" fontId="6" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="9"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="9"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="9"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -1990,17 +2467,13 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2014,32 +2487,8 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2062,457 +2511,8 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="9"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="9"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="9"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="5" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="38" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -2946,28 +2946,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="114"/>
+      <c r="B1" s="85"/>
     </row>
     <row r="2" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="114"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="102" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="104"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="131"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="132"/>
       <c r="P2" s="17" t="s">
         <v>3</v>
       </c>
@@ -2977,21 +2977,21 @@
       <c r="R2" s="17"/>
     </row>
     <row r="3" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="125" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="107"/>
+      <c r="C3" s="133"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="134"/>
+      <c r="M3" s="134"/>
+      <c r="N3" s="135"/>
       <c r="O3" s="3"/>
       <c r="P3" s="17" t="s">
         <v>4</v>
@@ -3002,19 +3002,19 @@
       <c r="R3" s="17"/>
     </row>
     <row r="4" spans="1:19" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="100"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="109"/>
-      <c r="L4" s="109"/>
-      <c r="M4" s="109"/>
-      <c r="N4" s="110"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137"/>
+      <c r="M4" s="137"/>
+      <c r="N4" s="138"/>
       <c r="O4" s="3"/>
       <c r="P4" s="17" t="s">
         <v>11</v>
@@ -3031,15 +3031,15 @@
       <c r="C5" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="166" t="s">
+      <c r="D5" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="111" t="s">
+      <c r="E5" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="112"/>
-      <c r="G5" s="112"/>
-      <c r="H5" s="113"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="141"/>
       <c r="I5" s="21" t="s">
         <v>35</v>
       </c>
@@ -3072,16 +3072,16 @@
       <c r="C6" s="49">
         <v>46314</v>
       </c>
-      <c r="D6" s="168" t="s">
+      <c r="D6" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="89" t="str">
+      <c r="E6" s="82" t="str">
         <f>IFERROR(VLOOKUP(B6,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="91"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="84"/>
       <c r="I6" s="7">
         <v>66</v>
       </c>
@@ -3092,16 +3092,16 @@
         <f>J6/I6</f>
         <v>1.303030303030303</v>
       </c>
-      <c r="L6" s="162">
+      <c r="L6" s="64">
         <v>4650</v>
       </c>
-      <c r="M6" s="175">
+      <c r="M6" s="73">
         <v>14632901001</v>
       </c>
-      <c r="N6" s="176"/>
-      <c r="O6" s="177"/>
-      <c r="P6" s="177"/>
-      <c r="Q6" s="177"/>
+      <c r="N6" s="145"/>
+      <c r="O6" s="146"/>
+      <c r="P6" s="146"/>
+      <c r="Q6" s="146"/>
       <c r="R6" s="17"/>
       <c r="S6" s="1"/>
     </row>
@@ -3115,13 +3115,13 @@
       <c r="D7" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="89" t="str">
+      <c r="E7" s="82" t="str">
         <f>IFERROR(VLOOKUP(B7,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F7" s="90"/>
-      <c r="G7" s="90"/>
-      <c r="H7" s="91"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="84"/>
       <c r="I7" s="7">
         <v>86</v>
       </c>
@@ -3132,16 +3132,16 @@
         <f>J7/I7</f>
         <v>1.0116279069767442</v>
       </c>
-      <c r="L7" s="162">
+      <c r="L7" s="64">
         <v>5400</v>
       </c>
-      <c r="M7" s="175">
+      <c r="M7" s="73">
         <v>14632601001</v>
       </c>
-      <c r="N7" s="176"/>
-      <c r="O7" s="177"/>
-      <c r="P7" s="177"/>
-      <c r="Q7" s="177"/>
+      <c r="N7" s="145"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="146"/>
+      <c r="Q7" s="146"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
@@ -3155,13 +3155,13 @@
       <c r="D8" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="89" t="str">
+      <c r="E8" s="82" t="str">
         <f>IFERROR(VLOOKUP(B8,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="91"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="84"/>
       <c r="I8" s="11">
         <v>13</v>
       </c>
@@ -3172,16 +3172,16 @@
         <f>J8/I8</f>
         <v>1.8461538461538463</v>
       </c>
-      <c r="L8" s="162">
+      <c r="L8" s="64">
         <v>780</v>
       </c>
-      <c r="M8" s="175">
+      <c r="M8" s="73">
         <v>14632801001</v>
       </c>
-      <c r="N8" s="178"/>
-      <c r="O8" s="179"/>
-      <c r="P8" s="179"/>
-      <c r="Q8" s="179"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="75"/>
+      <c r="P8" s="75"/>
+      <c r="Q8" s="75"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
@@ -3195,13 +3195,13 @@
       <c r="D9" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="89" t="str">
+      <c r="E9" s="82" t="str">
         <f>IFERROR(VLOOKUP(B9,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="91"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="84"/>
       <c r="I9" s="7">
         <v>61</v>
       </c>
@@ -3215,29 +3215,29 @@
       <c r="L9" s="24">
         <v>3720</v>
       </c>
-      <c r="M9" s="133">
+      <c r="M9" s="56">
         <v>14632701001</v>
       </c>
-      <c r="N9" s="180" t="s">
+      <c r="N9" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="O9" s="181"/>
-      <c r="P9" s="181"/>
-      <c r="Q9" s="182"/>
+      <c r="O9" s="77"/>
+      <c r="P9" s="77"/>
+      <c r="Q9" s="78"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
-      <c r="C10" s="165"/>
+      <c r="C10" s="65"/>
       <c r="D10" s="36"/>
-      <c r="E10" s="89" t="str">
+      <c r="E10" s="82" t="str">
         <f>IFERROR(VLOOKUP(B10,'base itens'!A:B,2,0),"")</f>
         <v/>
       </c>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="91"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="84"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="16" t="e">
@@ -3245,112 +3245,112 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L10" s="24"/>
-      <c r="M10" s="133"/>
-      <c r="N10" s="180"/>
-      <c r="O10" s="181"/>
-      <c r="P10" s="181"/>
-      <c r="Q10" s="182"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="76"/>
+      <c r="O10" s="77"/>
+      <c r="P10" s="77"/>
+      <c r="Q10" s="78"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="134"/>
-      <c r="C11" s="165"/>
-      <c r="D11" s="169"/>
-      <c r="E11" s="89" t="str">
+      <c r="B11" s="57"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="82" t="str">
         <f>IFERROR(VLOOKUP(B11,'base itens'!A:B,2,0),"")</f>
         <v/>
       </c>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="135"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
       <c r="K11" s="16" t="e">
-        <f t="shared" ref="K10:K11" si="0">J11/I11</f>
+        <f t="shared" ref="K11" si="0">J11/I11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L11" s="136"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="180"/>
-      <c r="O11" s="181"/>
-      <c r="P11" s="181"/>
-      <c r="Q11" s="182"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="76"/>
+      <c r="O11" s="77"/>
+      <c r="P11" s="77"/>
+      <c r="Q11" s="78"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="143" t="s">
+      <c r="B12" s="98" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="143"/>
-      <c r="D12" s="167"/>
-      <c r="E12" s="143"/>
-      <c r="F12" s="143"/>
-      <c r="G12" s="143"/>
-      <c r="H12" s="143"/>
-      <c r="I12" s="143"/>
-      <c r="J12" s="143"/>
-      <c r="K12" s="143"/>
-      <c r="L12" s="143"/>
-      <c r="M12" s="143"/>
-      <c r="N12" s="167"/>
-      <c r="O12" s="167"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="98"/>
+      <c r="N12" s="99"/>
+      <c r="O12" s="99"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="18"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="146"/>
-      <c r="C13" s="164"/>
-      <c r="D13" s="144" t="s">
+      <c r="B13" s="100"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="149" t="s">
+      <c r="E13" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="149"/>
-      <c r="G13" s="149"/>
-      <c r="H13" s="150"/>
-      <c r="I13" s="145" t="s">
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="63" t="s">
         <v>151</v>
       </c>
-      <c r="J13" s="145" t="s">
+      <c r="J13" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="K13" s="161"/>
-      <c r="L13" s="149"/>
-      <c r="M13" s="149"/>
-      <c r="N13" s="149"/>
-      <c r="O13" s="144"/>
+      <c r="K13" s="107"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="105"/>
+      <c r="N13" s="105"/>
+      <c r="O13" s="62"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="18"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="147"/>
-      <c r="C14" s="151"/>
-      <c r="D14" s="168" t="s">
+      <c r="B14" s="101"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="138" t="s">
+      <c r="E14" s="142" t="s">
         <v>104</v>
       </c>
-      <c r="F14" s="139"/>
-      <c r="G14" s="139"/>
-      <c r="H14" s="140"/>
-      <c r="I14" s="141">
+      <c r="F14" s="143"/>
+      <c r="G14" s="143"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="60">
         <v>285</v>
       </c>
       <c r="J14" s="12"/>
-      <c r="K14" s="142" t="s">
+      <c r="K14" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="L14" s="152"/>
-      <c r="M14" s="153"/>
-      <c r="N14" s="154"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="109"/>
+      <c r="N14" s="110"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="18"/>
@@ -3358,27 +3358,27 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="147"/>
-      <c r="C15" s="151"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="104"/>
       <c r="D15" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="92" t="s">
+      <c r="E15" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="92"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
       <c r="I15" s="7">
         <v>168</v>
       </c>
       <c r="J15" s="7"/>
-      <c r="K15" s="142" t="s">
+      <c r="K15" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="L15" s="155"/>
-      <c r="M15" s="156"/>
-      <c r="N15" s="157"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="113"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="18"/>
@@ -3386,27 +3386,27 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19" s="5" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="148"/>
-      <c r="C16" s="151"/>
-      <c r="D16" s="169" t="s">
+      <c r="B16" s="102"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="92" t="s">
+      <c r="E16" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="92"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="92"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="117"/>
       <c r="I16" s="7">
         <v>282</v>
       </c>
       <c r="J16" s="7"/>
-      <c r="K16" s="142" t="s">
+      <c r="K16" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="L16" s="158"/>
-      <c r="M16" s="159"/>
-      <c r="N16" s="160"/>
+      <c r="L16" s="114"/>
+      <c r="M16" s="115"/>
+      <c r="N16" s="116"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="18"/>
@@ -3414,21 +3414,21 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="93" t="s">
+      <c r="B17" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="163"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="94"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="94"/>
-      <c r="N17" s="95"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="120"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="121"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="18"/>
@@ -3440,27 +3440,27 @@
         <v>5</v>
       </c>
       <c r="C18" s="31"/>
-      <c r="D18" s="130" t="s">
+      <c r="D18" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="66" t="s">
+      <c r="E18" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
-      <c r="H18" s="101"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="128"/>
+      <c r="H18" s="129"/>
       <c r="I18" s="31" t="s">
         <v>41</v>
       </c>
       <c r="J18" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="K18" s="96" t="s">
+      <c r="K18" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="L18" s="97"/>
-      <c r="M18" s="97"/>
-      <c r="N18" s="98"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="123"/>
+      <c r="N18" s="124"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="18"/>
@@ -3474,30 +3474,30 @@
       <c r="C19" s="49">
         <v>46314</v>
       </c>
-      <c r="D19" s="168" t="s">
+      <c r="D19" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="89" t="str">
+      <c r="E19" s="82" t="str">
         <f>IFERROR(VLOOKUP(B19,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="91"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="84"/>
       <c r="I19" s="41">
         <v>86</v>
       </c>
       <c r="J19" s="34">
         <v>0.52300000000000002</v>
       </c>
-      <c r="K19" s="50" t="s">
+      <c r="K19" s="157" t="s">
         <v>142</v>
       </c>
-      <c r="L19" s="51"/>
-      <c r="M19" s="185"/>
-      <c r="N19" s="183"/>
-      <c r="O19" s="184"/>
-      <c r="P19" s="186"/>
+      <c r="L19" s="158"/>
+      <c r="M19" s="159"/>
+      <c r="N19" s="79"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="81"/>
       <c r="Q19" s="18"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
@@ -3512,24 +3512,24 @@
       <c r="D20" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="89" t="str">
+      <c r="E20" s="82" t="str">
         <f>IFERROR(VLOOKUP(B20,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="91"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="84"/>
       <c r="I20" s="41">
         <v>87</v>
       </c>
       <c r="J20" s="34">
         <v>0.52700000000000002</v>
       </c>
-      <c r="K20" s="50" t="s">
+      <c r="K20" s="157" t="s">
         <v>142</v>
       </c>
-      <c r="L20" s="51"/>
-      <c r="M20" s="51"/>
+      <c r="L20" s="158"/>
+      <c r="M20" s="158"/>
       <c r="N20" s="32"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -3547,24 +3547,24 @@
       <c r="D21" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="89" t="str">
+      <c r="E21" s="82" t="str">
         <f>IFERROR(VLOOKUP(B21,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="91"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="84"/>
       <c r="I21" s="41">
         <v>24</v>
       </c>
       <c r="J21" s="34">
         <v>0.52700000000000002</v>
       </c>
-      <c r="K21" s="50" t="s">
+      <c r="K21" s="157" t="s">
         <v>142</v>
       </c>
-      <c r="L21" s="51"/>
-      <c r="M21" s="51"/>
+      <c r="L21" s="158"/>
+      <c r="M21" s="158"/>
       <c r="N21" s="32"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
@@ -3582,24 +3582,24 @@
       <c r="D22" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="89" t="str">
+      <c r="E22" s="82" t="str">
         <f>IFERROR(VLOOKUP(B22,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="91"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="84"/>
       <c r="I22" s="41">
         <v>48</v>
       </c>
       <c r="J22" s="34">
         <v>0.52700000000000002</v>
       </c>
-      <c r="K22" s="50" t="s">
+      <c r="K22" s="157" t="s">
         <v>142</v>
       </c>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51"/>
+      <c r="L22" s="158"/>
+      <c r="M22" s="158"/>
       <c r="N22" s="32"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -3611,15 +3611,15 @@
       <c r="B23" s="6"/>
       <c r="C23" s="49"/>
       <c r="D23" s="36"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="91"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="84"/>
       <c r="I23" s="41"/>
       <c r="J23" s="34"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="51"/>
-      <c r="M23" s="51"/>
+      <c r="K23" s="157"/>
+      <c r="L23" s="158"/>
+      <c r="M23" s="158"/>
       <c r="N23" s="32"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -3628,21 +3628,21 @@
       <c r="S23" s="1"/>
     </row>
     <row r="24" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="170"/>
-      <c r="C24" s="173"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="71"/>
       <c r="D24" s="36"/>
-      <c r="E24" s="89" t="str">
+      <c r="E24" s="82" t="str">
         <f>IFERROR(VLOOKUP(B24,'base itens'!A:B,2,0),"")</f>
         <v/>
       </c>
-      <c r="F24" s="90"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="91"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="84"/>
       <c r="I24" s="41"/>
       <c r="J24" s="34"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
+      <c r="K24" s="157"/>
+      <c r="L24" s="158"/>
+      <c r="M24" s="158"/>
       <c r="N24" s="32"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -3651,18 +3651,18 @@
       <c r="S24" s="1"/>
     </row>
     <row r="25" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="170"/>
-      <c r="C25" s="173"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="71"/>
       <c r="D25" s="36"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="63"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="155"/>
+      <c r="G25" s="155"/>
+      <c r="H25" s="156"/>
       <c r="I25" s="43"/>
       <c r="J25" s="34"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="51"/>
-      <c r="M25" s="51"/>
+      <c r="K25" s="157"/>
+      <c r="L25" s="158"/>
+      <c r="M25" s="158"/>
       <c r="N25" s="32"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -3671,269 +3671,266 @@
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="2:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="171" t="str">
+      <c r="B26" s="70" t="str">
         <f>IF(B15&gt;0,B15,"")</f>
         <v/>
       </c>
-      <c r="C26" s="174"/>
-      <c r="D26" s="169"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="84"/>
-      <c r="G26" s="84"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="7" t="str">
-        <f t="shared" ref="I26" si="1">IF(J15&gt;0,J15,"")</f>
-        <v/>
-      </c>
+      <c r="C26" s="72"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="148"/>
+      <c r="G26" s="148"/>
+      <c r="H26" s="149"/>
+      <c r="I26" s="7"/>
       <c r="J26" s="33"/>
-      <c r="K26" s="73"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
+      <c r="K26" s="175"/>
+      <c r="L26" s="176"/>
+      <c r="M26" s="176"/>
       <c r="N26" s="47"/>
     </row>
     <row r="27" spans="2:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="86" t="s">
+      <c r="B27" s="150" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="172"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="87"/>
-      <c r="H27" s="87"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="87"/>
-      <c r="N27" s="88"/>
+      <c r="C27" s="151"/>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="152"/>
+      <c r="G27" s="152"/>
+      <c r="H27" s="152"/>
+      <c r="I27" s="152"/>
+      <c r="J27" s="152"/>
+      <c r="K27" s="152"/>
+      <c r="L27" s="152"/>
+      <c r="M27" s="152"/>
+      <c r="N27" s="153"/>
     </row>
     <row r="28" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="160" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="75" t="s">
+      <c r="C28" s="161"/>
+      <c r="D28" s="161"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="160" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="77"/>
-      <c r="K28" s="75" t="s">
+      <c r="G28" s="161"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="161"/>
+      <c r="J28" s="162"/>
+      <c r="K28" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="L28" s="76"/>
-      <c r="M28" s="76"/>
-      <c r="N28" s="77"/>
+      <c r="L28" s="161"/>
+      <c r="M28" s="161"/>
+      <c r="N28" s="162"/>
     </row>
     <row r="29" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="80" t="s">
+      <c r="C29" s="163" t="s">
         <v>15</v>
       </c>
-      <c r="D29" s="82"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="78" t="s">
+      <c r="D29" s="164"/>
+      <c r="E29" s="165"/>
+      <c r="F29" s="166" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="82"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="80" t="s">
+      <c r="G29" s="164"/>
+      <c r="H29" s="167"/>
+      <c r="I29" s="163" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="81"/>
-      <c r="K29" s="78" t="s">
+      <c r="J29" s="165"/>
+      <c r="K29" s="166" t="s">
         <v>69</v>
       </c>
-      <c r="L29" s="79"/>
-      <c r="M29" s="80" t="s">
+      <c r="L29" s="167"/>
+      <c r="M29" s="163" t="s">
         <v>15</v>
       </c>
-      <c r="N29" s="81"/>
+      <c r="N29" s="165"/>
     </row>
     <row r="30" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="64" t="s">
+      <c r="C30" s="168" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="56"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="55" t="s">
+      <c r="D30" s="169"/>
+      <c r="E30" s="170"/>
+      <c r="F30" s="171" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="56"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="53" t="s">
+      <c r="G30" s="169"/>
+      <c r="H30" s="172"/>
+      <c r="I30" s="173" t="s">
         <v>63</v>
       </c>
-      <c r="J30" s="54"/>
-      <c r="K30" s="55" t="s">
+      <c r="J30" s="174"/>
+      <c r="K30" s="171" t="s">
         <v>98</v>
       </c>
-      <c r="L30" s="57"/>
-      <c r="M30" s="53" t="s">
+      <c r="L30" s="172"/>
+      <c r="M30" s="173" t="s">
         <v>68</v>
       </c>
-      <c r="N30" s="54"/>
+      <c r="N30" s="174"/>
     </row>
     <row r="31" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="37"/>
-      <c r="C31" s="64"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="54"/>
+      <c r="C31" s="168"/>
+      <c r="D31" s="169"/>
+      <c r="E31" s="170"/>
+      <c r="F31" s="171"/>
+      <c r="G31" s="169"/>
+      <c r="H31" s="172"/>
+      <c r="I31" s="173"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="171"/>
+      <c r="L31" s="172"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="174"/>
     </row>
     <row r="32" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="37"/>
-      <c r="C32" s="64"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="55"/>
-      <c r="L32" s="57"/>
-      <c r="M32" s="53"/>
-      <c r="N32" s="54"/>
+      <c r="C32" s="168"/>
+      <c r="D32" s="169"/>
+      <c r="E32" s="170"/>
+      <c r="F32" s="171"/>
+      <c r="G32" s="169"/>
+      <c r="H32" s="172"/>
+      <c r="I32" s="173"/>
+      <c r="J32" s="174"/>
+      <c r="K32" s="171"/>
+      <c r="L32" s="172"/>
+      <c r="M32" s="173"/>
+      <c r="N32" s="174"/>
     </row>
     <row r="33" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="37"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="65"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="57"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="54"/>
+      <c r="C33" s="168"/>
+      <c r="D33" s="169"/>
+      <c r="E33" s="170"/>
+      <c r="F33" s="171"/>
+      <c r="G33" s="169"/>
+      <c r="H33" s="172"/>
+      <c r="I33" s="173"/>
+      <c r="J33" s="174"/>
+      <c r="K33" s="171"/>
+      <c r="L33" s="172"/>
+      <c r="M33" s="173"/>
+      <c r="N33" s="174"/>
     </row>
     <row r="34" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="37"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="54"/>
-      <c r="K34" s="55"/>
-      <c r="L34" s="57"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="54"/>
+      <c r="C34" s="168"/>
+      <c r="D34" s="169"/>
+      <c r="E34" s="170"/>
+      <c r="F34" s="171"/>
+      <c r="G34" s="169"/>
+      <c r="H34" s="172"/>
+      <c r="I34" s="173"/>
+      <c r="J34" s="174"/>
+      <c r="K34" s="171"/>
+      <c r="L34" s="172"/>
+      <c r="M34" s="173"/>
+      <c r="N34" s="174"/>
     </row>
     <row r="35" spans="2:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="38"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="54"/>
-      <c r="K35" s="55"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="54"/>
+      <c r="C35" s="168"/>
+      <c r="D35" s="169"/>
+      <c r="E35" s="170"/>
+      <c r="F35" s="171"/>
+      <c r="G35" s="169"/>
+      <c r="H35" s="172"/>
+      <c r="I35" s="173"/>
+      <c r="J35" s="174"/>
+      <c r="K35" s="171"/>
+      <c r="L35" s="172"/>
+      <c r="M35" s="173"/>
+      <c r="N35" s="174"/>
     </row>
     <row r="36" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="70" t="s">
+      <c r="B36" s="183" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="71"/>
-      <c r="M36" s="71"/>
-      <c r="N36" s="72"/>
+      <c r="C36" s="184"/>
+      <c r="D36" s="184"/>
+      <c r="E36" s="184"/>
+      <c r="F36" s="184"/>
+      <c r="G36" s="184"/>
+      <c r="H36" s="184"/>
+      <c r="I36" s="184"/>
+      <c r="J36" s="184"/>
+      <c r="K36" s="184"/>
+      <c r="L36" s="184"/>
+      <c r="M36" s="184"/>
+      <c r="N36" s="185"/>
       <c r="S36" s="8"/>
     </row>
     <row r="37" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="129" t="s">
+      <c r="B37" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="130" t="s">
+      <c r="C37" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="130" t="s">
+      <c r="D37" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="E37" s="69" t="s">
+      <c r="E37" s="182" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
+      <c r="F37" s="182"/>
+      <c r="G37" s="182"/>
+      <c r="H37" s="182"/>
       <c r="I37" s="27" t="s">
         <v>73</v>
       </c>
       <c r="J37" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="K37" s="66" t="s">
+      <c r="K37" s="127" t="s">
         <v>15</v>
       </c>
-      <c r="L37" s="67"/>
-      <c r="M37" s="67"/>
-      <c r="N37" s="68"/>
+      <c r="L37" s="128"/>
+      <c r="M37" s="128"/>
+      <c r="N37" s="181"/>
       <c r="S37" s="8"/>
     </row>
     <row r="38" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="125">
+      <c r="C38" s="51">
         <v>46314</v>
       </c>
-      <c r="D38" s="127" t="s">
+      <c r="D38" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="128" t="s">
+      <c r="E38" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="128"/>
-      <c r="G38" s="128"/>
-      <c r="H38" s="128"/>
+      <c r="F38" s="180"/>
+      <c r="G38" s="180"/>
+      <c r="H38" s="180"/>
       <c r="I38" s="29">
         <v>0</v>
       </c>
       <c r="J38" s="29">
         <v>0</v>
       </c>
-      <c r="K38" s="58" t="s">
+      <c r="K38" s="177" t="s">
         <v>135</v>
       </c>
-      <c r="L38" s="59"/>
-      <c r="M38" s="59"/>
-      <c r="N38" s="60"/>
+      <c r="L38" s="178"/>
+      <c r="M38" s="178"/>
+      <c r="N38" s="179"/>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
       <c r="Q38" s="19"/>
@@ -3944,30 +3941,30 @@
       <c r="B39" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="125">
+      <c r="C39" s="51">
         <v>46314</v>
       </c>
-      <c r="D39" s="127" t="s">
+      <c r="D39" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="128" t="s">
+      <c r="E39" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F39" s="128"/>
-      <c r="G39" s="128"/>
-      <c r="H39" s="128"/>
+      <c r="F39" s="180"/>
+      <c r="G39" s="180"/>
+      <c r="H39" s="180"/>
       <c r="I39" s="29">
         <v>0</v>
       </c>
       <c r="J39" s="29">
         <v>0</v>
       </c>
-      <c r="K39" s="58" t="s">
+      <c r="K39" s="177" t="s">
         <v>135</v>
       </c>
-      <c r="L39" s="59"/>
-      <c r="M39" s="59"/>
-      <c r="N39" s="60"/>
+      <c r="L39" s="178"/>
+      <c r="M39" s="178"/>
+      <c r="N39" s="179"/>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
       <c r="Q39" s="19"/>
@@ -3978,30 +3975,30 @@
       <c r="B40" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="125">
+      <c r="C40" s="51">
         <v>46314</v>
       </c>
-      <c r="D40" s="127" t="s">
+      <c r="D40" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="E40" s="128" t="s">
+      <c r="E40" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F40" s="128"/>
-      <c r="G40" s="128"/>
-      <c r="H40" s="128"/>
+      <c r="F40" s="180"/>
+      <c r="G40" s="180"/>
+      <c r="H40" s="180"/>
       <c r="I40" s="29">
         <v>0</v>
       </c>
       <c r="J40" s="29">
         <v>0</v>
       </c>
-      <c r="K40" s="58" t="s">
+      <c r="K40" s="177" t="s">
         <v>135</v>
       </c>
-      <c r="L40" s="59"/>
-      <c r="M40" s="59"/>
-      <c r="N40" s="60"/>
+      <c r="L40" s="178"/>
+      <c r="M40" s="178"/>
+      <c r="N40" s="179"/>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
       <c r="Q40" s="19"/>
@@ -4010,18 +4007,18 @@
     </row>
     <row r="41" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="7"/>
-      <c r="C41" s="126"/>
-      <c r="D41" s="127"/>
-      <c r="E41" s="128"/>
-      <c r="F41" s="128"/>
-      <c r="G41" s="128"/>
-      <c r="H41" s="128"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="180"/>
+      <c r="F41" s="180"/>
+      <c r="G41" s="180"/>
+      <c r="H41" s="180"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="59"/>
-      <c r="M41" s="59"/>
-      <c r="N41" s="60"/>
+      <c r="K41" s="177"/>
+      <c r="L41" s="178"/>
+      <c r="M41" s="178"/>
+      <c r="N41" s="179"/>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
       <c r="Q41" s="19"/>
@@ -4029,21 +4026,21 @@
       <c r="S41" s="8"/>
     </row>
     <row r="42" spans="2:19" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="B42" s="122" t="s">
+      <c r="B42" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="123"/>
-      <c r="D42" s="123"/>
-      <c r="E42" s="123"/>
-      <c r="F42" s="123"/>
-      <c r="G42" s="123"/>
-      <c r="H42" s="123"/>
-      <c r="I42" s="124"/>
-      <c r="J42" s="131"/>
-      <c r="K42" s="123"/>
-      <c r="L42" s="123"/>
-      <c r="M42" s="123"/>
-      <c r="N42" s="132"/>
+      <c r="C42" s="94"/>
+      <c r="D42" s="94"/>
+      <c r="E42" s="94"/>
+      <c r="F42" s="94"/>
+      <c r="G42" s="94"/>
+      <c r="H42" s="94"/>
+      <c r="I42" s="95"/>
+      <c r="J42" s="96"/>
+      <c r="K42" s="94"/>
+      <c r="L42" s="94"/>
+      <c r="M42" s="94"/>
+      <c r="N42" s="97"/>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
       <c r="Q42" s="19"/>
@@ -4060,20 +4057,20 @@
       <c r="D43" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="E43" s="52" t="s">
+      <c r="E43" s="186" t="s">
         <v>6</v>
       </c>
-      <c r="F43" s="52"/>
-      <c r="G43" s="52"/>
-      <c r="H43" s="52"/>
+      <c r="F43" s="186"/>
+      <c r="G43" s="186"/>
+      <c r="H43" s="186"/>
       <c r="I43" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="J43" s="115"/>
-      <c r="K43" s="116"/>
-      <c r="L43" s="116"/>
-      <c r="M43" s="116"/>
-      <c r="N43" s="117"/>
+      <c r="J43" s="90"/>
+      <c r="K43" s="91"/>
+      <c r="L43" s="91"/>
+      <c r="M43" s="91"/>
+      <c r="N43" s="92"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="17"/>
@@ -4084,26 +4081,26 @@
       <c r="B44" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="125">
+      <c r="C44" s="51">
         <v>46314</v>
       </c>
-      <c r="D44" s="127" t="s">
+      <c r="D44" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="128" t="s">
+      <c r="E44" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F44" s="128"/>
-      <c r="G44" s="128"/>
-      <c r="H44" s="128"/>
+      <c r="F44" s="180"/>
+      <c r="G44" s="180"/>
+      <c r="H44" s="180"/>
       <c r="I44" s="29">
         <v>1137</v>
       </c>
-      <c r="J44" s="118"/>
-      <c r="K44" s="119"/>
-      <c r="L44" s="119"/>
-      <c r="M44" s="119"/>
-      <c r="N44" s="119"/>
+      <c r="J44" s="86"/>
+      <c r="K44" s="87"/>
+      <c r="L44" s="87"/>
+      <c r="M44" s="87"/>
+      <c r="N44" s="87"/>
       <c r="O44" s="48">
         <v>14003101001</v>
       </c>
@@ -4120,26 +4117,26 @@
       <c r="B45" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="125">
+      <c r="C45" s="51">
         <v>46314</v>
       </c>
-      <c r="D45" s="127" t="s">
+      <c r="D45" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="128" t="s">
+      <c r="E45" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F45" s="128"/>
-      <c r="G45" s="128"/>
-      <c r="H45" s="128"/>
+      <c r="F45" s="180"/>
+      <c r="G45" s="180"/>
+      <c r="H45" s="180"/>
       <c r="I45" s="29">
         <v>1417.5</v>
       </c>
-      <c r="J45" s="120"/>
-      <c r="K45" s="121"/>
-      <c r="L45" s="121"/>
-      <c r="M45" s="121"/>
-      <c r="N45" s="121"/>
+      <c r="J45" s="88"/>
+      <c r="K45" s="89"/>
+      <c r="L45" s="89"/>
+      <c r="M45" s="89"/>
+      <c r="N45" s="89"/>
       <c r="O45" s="7">
         <v>14003201001</v>
       </c>
@@ -4156,26 +4153,26 @@
       <c r="B46" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="125">
+      <c r="C46" s="51">
         <v>46314</v>
       </c>
-      <c r="D46" s="127" t="s">
+      <c r="D46" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="E46" s="128" t="s">
+      <c r="E46" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F46" s="128"/>
-      <c r="G46" s="128"/>
-      <c r="H46" s="128"/>
+      <c r="F46" s="180"/>
+      <c r="G46" s="180"/>
+      <c r="H46" s="180"/>
       <c r="I46" s="29">
         <v>454</v>
       </c>
-      <c r="J46" s="120"/>
-      <c r="K46" s="121"/>
-      <c r="L46" s="121"/>
-      <c r="M46" s="121"/>
-      <c r="N46" s="121"/>
+      <c r="J46" s="88"/>
+      <c r="K46" s="89"/>
+      <c r="L46" s="89"/>
+      <c r="M46" s="89"/>
+      <c r="N46" s="89"/>
       <c r="O46" s="7">
         <v>13978401001</v>
       </c>
@@ -4192,60 +4189,60 @@
       <c r="B47" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="125">
+      <c r="C47" s="51">
         <v>46314</v>
       </c>
-      <c r="D47" s="127" t="s">
+      <c r="D47" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="128" t="s">
+      <c r="E47" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F47" s="128"/>
-      <c r="G47" s="128"/>
-      <c r="H47" s="128"/>
+      <c r="F47" s="180"/>
+      <c r="G47" s="180"/>
+      <c r="H47" s="180"/>
       <c r="I47" s="29">
         <v>1098</v>
       </c>
-      <c r="J47" s="120"/>
-      <c r="K47" s="121"/>
-      <c r="L47" s="121"/>
-      <c r="M47" s="121"/>
-      <c r="N47" s="121"/>
+      <c r="J47" s="88"/>
+      <c r="K47" s="89"/>
+      <c r="L47" s="89"/>
+      <c r="M47" s="89"/>
+      <c r="N47" s="89"/>
       <c r="O47" s="4"/>
     </row>
     <row r="48" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B48" s="7"/>
-      <c r="C48" s="125"/>
-      <c r="D48" s="127"/>
-      <c r="E48" s="128"/>
-      <c r="F48" s="128"/>
-      <c r="G48" s="128"/>
-      <c r="H48" s="128"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="180"/>
+      <c r="F48" s="180"/>
+      <c r="G48" s="180"/>
+      <c r="H48" s="180"/>
       <c r="I48" s="29"/>
-      <c r="J48" s="120"/>
-      <c r="K48" s="121"/>
-      <c r="L48" s="121"/>
-      <c r="M48" s="121"/>
-      <c r="N48" s="121"/>
+      <c r="J48" s="88"/>
+      <c r="K48" s="89"/>
+      <c r="L48" s="89"/>
+      <c r="M48" s="89"/>
+      <c r="N48" s="89"/>
       <c r="O48" s="4">
         <v>13851401001</v>
       </c>
     </row>
     <row r="49" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B49" s="125"/>
-      <c r="C49" s="126"/>
-      <c r="D49" s="127"/>
-      <c r="E49" s="92"/>
-      <c r="F49" s="92"/>
-      <c r="G49" s="92"/>
-      <c r="H49" s="92"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="117"/>
+      <c r="G49" s="117"/>
+      <c r="H49" s="117"/>
       <c r="I49" s="29"/>
-      <c r="J49" s="120"/>
-      <c r="K49" s="121"/>
-      <c r="L49" s="121"/>
-      <c r="M49" s="121"/>
-      <c r="N49" s="121"/>
+      <c r="J49" s="88"/>
+      <c r="K49" s="89"/>
+      <c r="L49" s="89"/>
+      <c r="M49" s="89"/>
+      <c r="N49" s="89"/>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.3"/>
     <row r="51" spans="2:14" x14ac:dyDescent="0.3"/>
@@ -4343,6 +4340,83 @@
     <row r="143" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K41:N41"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="B36:N36"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:J28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="B27:N27"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K26:M26"/>
     <mergeCell ref="E11:H11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="J44:N49"/>
@@ -4367,83 +4441,6 @@
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="N7:Q7"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="B27:N27"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:J28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="K37:N37"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="B36:N36"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K41:N41"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="2">
@@ -7165,6 +7162,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="86c6d835-384d-4eee-b5e4-7a7d42cb3d19" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004A4A59D84FFE1748BB38BBBF60A87067" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="122dd576e940e33e9bdee9d882a1d0b8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="86c6d835-384d-4eee-b5e4-7a7d42cb3d19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ef1bdbddccf683fbaa0b0495f4025495" ns3:_="">
     <xsd:import namespace="86c6d835-384d-4eee-b5e4-7a7d42cb3d19"/>
@@ -7320,24 +7334,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54BB2CB7-F996-4C7B-B8F6-D759D6846113}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="86c6d835-384d-4eee-b5e4-7a7d42cb3d19"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="86c6d835-384d-4eee-b5e4-7a7d42cb3d19" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{601125AE-989D-4A8E-B764-68DA4A2ACCDA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A98C6C55-1841-4DCB-B412-B1F89DBD7BD9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7353,28 +7374,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{601125AE-989D-4A8E-B764-68DA4A2ACCDA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54BB2CB7-F996-4C7B-B8F6-D759D6846113}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="86c6d835-384d-4eee-b5e4-7a7d42cb3d19"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/api/_modelo_report.xlsx
+++ b/api/_modelo_report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego.batista\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego.batista\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D2B288-5818-40DF-9E66-9D9C5AC8ABDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C774446-84B2-4753-AB52-5C4FFD3205C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" xr2:uid="{A61D48FF-59C3-42AE-88A3-50A1935DB5F5}"/>
   </bookViews>
@@ -1970,9 +1970,305 @@
     <xf numFmtId="14" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="9"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="9"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="9"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="14" fontId="33" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1985,6 +2281,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -1993,6 +2293,14 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2007,6 +2315,22 @@
     </xf>
     <xf numFmtId="2" fontId="6" fillId="5" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2017,11 +2341,79 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -2029,11 +2421,23 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="14" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2052,6 +2456,10 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="14" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2069,6 +2477,14 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2092,427 +2508,11 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="9"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="9"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="9"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -2946,28 +2946,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
+      <c r="B1" s="114"/>
     </row>
     <row r="2" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="130" t="s">
+      <c r="A2" s="114"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="131"/>
-      <c r="N2" s="132"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="104"/>
       <c r="P2" s="17" t="s">
         <v>3</v>
       </c>
@@ -2977,21 +2977,21 @@
       <c r="R2" s="17"/>
     </row>
     <row r="3" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="125" t="s">
+      <c r="B3" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="134"/>
-      <c r="M3" s="134"/>
-      <c r="N3" s="135"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="106"/>
+      <c r="N3" s="107"/>
       <c r="O3" s="3"/>
       <c r="P3" s="17" t="s">
         <v>4</v>
@@ -3002,19 +3002,19 @@
       <c r="R3" s="17"/>
     </row>
     <row r="4" spans="1:19" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="126"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="138"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="109"/>
+      <c r="L4" s="109"/>
+      <c r="M4" s="109"/>
+      <c r="N4" s="110"/>
       <c r="O4" s="3"/>
       <c r="P4" s="17" t="s">
         <v>11</v>
@@ -3031,15 +3031,15 @@
       <c r="C5" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="66" t="s">
+      <c r="D5" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="139" t="s">
+      <c r="E5" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="141"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="113"/>
       <c r="I5" s="21" t="s">
         <v>35</v>
       </c>
@@ -3072,16 +3072,16 @@
       <c r="C6" s="49">
         <v>46314</v>
       </c>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="82" t="str">
+      <c r="E6" s="89" t="str">
         <f>IFERROR(VLOOKUP(B6,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="84"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="91"/>
       <c r="I6" s="7">
         <v>66</v>
       </c>
@@ -3092,16 +3092,16 @@
         <f>J6/I6</f>
         <v>1.303030303030303</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="162">
         <v>4650</v>
       </c>
-      <c r="M6" s="73">
+      <c r="M6" s="175">
         <v>14632901001</v>
       </c>
-      <c r="N6" s="145"/>
-      <c r="O6" s="146"/>
-      <c r="P6" s="146"/>
-      <c r="Q6" s="146"/>
+      <c r="N6" s="176"/>
+      <c r="O6" s="177"/>
+      <c r="P6" s="177"/>
+      <c r="Q6" s="177"/>
       <c r="R6" s="17"/>
       <c r="S6" s="1"/>
     </row>
@@ -3115,13 +3115,13 @@
       <c r="D7" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="82" t="str">
+      <c r="E7" s="89" t="str">
         <f>IFERROR(VLOOKUP(B7,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="84"/>
+      <c r="F7" s="90"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="91"/>
       <c r="I7" s="7">
         <v>86</v>
       </c>
@@ -3132,16 +3132,16 @@
         <f>J7/I7</f>
         <v>1.0116279069767442</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="162">
         <v>5400</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="175">
         <v>14632601001</v>
       </c>
-      <c r="N7" s="145"/>
-      <c r="O7" s="146"/>
-      <c r="P7" s="146"/>
-      <c r="Q7" s="146"/>
+      <c r="N7" s="176"/>
+      <c r="O7" s="177"/>
+      <c r="P7" s="177"/>
+      <c r="Q7" s="177"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
@@ -3155,13 +3155,13 @@
       <c r="D8" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="82" t="str">
+      <c r="E8" s="89" t="str">
         <f>IFERROR(VLOOKUP(B8,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="84"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="91"/>
       <c r="I8" s="11">
         <v>13</v>
       </c>
@@ -3172,16 +3172,16 @@
         <f>J8/I8</f>
         <v>1.8461538461538463</v>
       </c>
-      <c r="L8" s="64">
+      <c r="L8" s="162">
         <v>780</v>
       </c>
-      <c r="M8" s="73">
+      <c r="M8" s="175">
         <v>14632801001</v>
       </c>
-      <c r="N8" s="74"/>
-      <c r="O8" s="75"/>
-      <c r="P8" s="75"/>
-      <c r="Q8" s="75"/>
+      <c r="N8" s="178"/>
+      <c r="O8" s="179"/>
+      <c r="P8" s="179"/>
+      <c r="Q8" s="179"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
@@ -3195,13 +3195,13 @@
       <c r="D9" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="82" t="str">
+      <c r="E9" s="89" t="str">
         <f>IFERROR(VLOOKUP(B9,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="84"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="91"/>
       <c r="I9" s="7">
         <v>61</v>
       </c>
@@ -3215,29 +3215,29 @@
       <c r="L9" s="24">
         <v>3720</v>
       </c>
-      <c r="M9" s="56">
+      <c r="M9" s="133">
         <v>14632701001</v>
       </c>
-      <c r="N9" s="76" t="s">
+      <c r="N9" s="180" t="s">
         <v>148</v>
       </c>
-      <c r="O9" s="77"/>
-      <c r="P9" s="77"/>
-      <c r="Q9" s="78"/>
+      <c r="O9" s="181"/>
+      <c r="P9" s="181"/>
+      <c r="Q9" s="182"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
-      <c r="C10" s="65"/>
+      <c r="C10" s="165"/>
       <c r="D10" s="36"/>
-      <c r="E10" s="82" t="str">
+      <c r="E10" s="89" t="str">
         <f>IFERROR(VLOOKUP(B10,'base itens'!A:B,2,0),"")</f>
         <v/>
       </c>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="84"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="91"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="16" t="e">
@@ -3245,112 +3245,112 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L10" s="24"/>
-      <c r="M10" s="56"/>
-      <c r="N10" s="76"/>
-      <c r="O10" s="77"/>
-      <c r="P10" s="77"/>
-      <c r="Q10" s="78"/>
+      <c r="M10" s="133"/>
+      <c r="N10" s="180"/>
+      <c r="O10" s="181"/>
+      <c r="P10" s="181"/>
+      <c r="Q10" s="182"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="57"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="82" t="str">
+      <c r="B11" s="134"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="169"/>
+      <c r="E11" s="89" t="str">
         <f>IFERROR(VLOOKUP(B11,'base itens'!A:B,2,0),"")</f>
         <v/>
       </c>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="135"/>
       <c r="K11" s="16" t="e">
-        <f t="shared" ref="K11" si="0">J11/I11</f>
+        <f t="shared" ref="K10:K11" si="0">J11/I11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L11" s="59"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="76"/>
-      <c r="O11" s="77"/>
-      <c r="P11" s="77"/>
-      <c r="Q11" s="78"/>
+      <c r="L11" s="136"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="180"/>
+      <c r="O11" s="181"/>
+      <c r="P11" s="181"/>
+      <c r="Q11" s="182"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="143" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="98"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="98"/>
-      <c r="N12" s="99"/>
-      <c r="O12" s="99"/>
+      <c r="C12" s="143"/>
+      <c r="D12" s="167"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="143"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="143"/>
+      <c r="L12" s="143"/>
+      <c r="M12" s="143"/>
+      <c r="N12" s="167"/>
+      <c r="O12" s="167"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="18"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="100"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="62" t="s">
+      <c r="B13" s="146"/>
+      <c r="C13" s="164"/>
+      <c r="D13" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="105" t="s">
+      <c r="E13" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="63" t="s">
+      <c r="F13" s="149"/>
+      <c r="G13" s="149"/>
+      <c r="H13" s="150"/>
+      <c r="I13" s="145" t="s">
         <v>151</v>
       </c>
-      <c r="J13" s="63" t="s">
+      <c r="J13" s="145" t="s">
         <v>152</v>
       </c>
-      <c r="K13" s="107"/>
-      <c r="L13" s="105"/>
-      <c r="M13" s="105"/>
-      <c r="N13" s="105"/>
-      <c r="O13" s="62"/>
+      <c r="K13" s="161"/>
+      <c r="L13" s="149"/>
+      <c r="M13" s="149"/>
+      <c r="N13" s="149"/>
+      <c r="O13" s="144"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="18"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="101"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="67" t="s">
+      <c r="B14" s="147"/>
+      <c r="C14" s="151"/>
+      <c r="D14" s="168" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="142" t="s">
+      <c r="E14" s="138" t="s">
         <v>104</v>
       </c>
-      <c r="F14" s="143"/>
-      <c r="G14" s="143"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="60">
+      <c r="F14" s="139"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="141">
         <v>285</v>
       </c>
       <c r="J14" s="12"/>
-      <c r="K14" s="61" t="s">
+      <c r="K14" s="142" t="s">
         <v>153</v>
       </c>
-      <c r="L14" s="108"/>
-      <c r="M14" s="109"/>
-      <c r="N14" s="110"/>
+      <c r="L14" s="152"/>
+      <c r="M14" s="153"/>
+      <c r="N14" s="154"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="18"/>
@@ -3358,27 +3358,27 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="101"/>
-      <c r="C15" s="104"/>
+      <c r="B15" s="147"/>
+      <c r="C15" s="151"/>
       <c r="D15" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="117" t="s">
+      <c r="E15" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="117"/>
+      <c r="F15" s="92"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
       <c r="I15" s="7">
         <v>168</v>
       </c>
       <c r="J15" s="7"/>
-      <c r="K15" s="61" t="s">
+      <c r="K15" s="142" t="s">
         <v>153</v>
       </c>
-      <c r="L15" s="111"/>
-      <c r="M15" s="112"/>
-      <c r="N15" s="113"/>
+      <c r="L15" s="155"/>
+      <c r="M15" s="156"/>
+      <c r="N15" s="157"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="18"/>
@@ -3386,27 +3386,27 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19" s="5" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="102"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="68" t="s">
+      <c r="B16" s="148"/>
+      <c r="C16" s="151"/>
+      <c r="D16" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="117" t="s">
+      <c r="E16" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
       <c r="I16" s="7">
         <v>282</v>
       </c>
       <c r="J16" s="7"/>
-      <c r="K16" s="61" t="s">
+      <c r="K16" s="142" t="s">
         <v>153</v>
       </c>
-      <c r="L16" s="114"/>
-      <c r="M16" s="115"/>
-      <c r="N16" s="116"/>
+      <c r="L16" s="158"/>
+      <c r="M16" s="159"/>
+      <c r="N16" s="160"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="18"/>
@@ -3414,21 +3414,21 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="118" t="s">
+      <c r="B17" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="119"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="120"/>
-      <c r="K17" s="120"/>
-      <c r="L17" s="120"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="121"/>
+      <c r="C17" s="163"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="94"/>
+      <c r="K17" s="94"/>
+      <c r="L17" s="94"/>
+      <c r="M17" s="94"/>
+      <c r="N17" s="95"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="18"/>
@@ -3440,27 +3440,27 @@
         <v>5</v>
       </c>
       <c r="C18" s="31"/>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="127" t="s">
+      <c r="E18" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="128"/>
-      <c r="G18" s="128"/>
-      <c r="H18" s="129"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="101"/>
       <c r="I18" s="31" t="s">
         <v>41</v>
       </c>
       <c r="J18" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="K18" s="122" t="s">
+      <c r="K18" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="L18" s="123"/>
-      <c r="M18" s="123"/>
-      <c r="N18" s="124"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="97"/>
+      <c r="N18" s="98"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="18"/>
@@ -3474,30 +3474,30 @@
       <c r="C19" s="49">
         <v>46314</v>
       </c>
-      <c r="D19" s="67" t="s">
+      <c r="D19" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="82" t="str">
+      <c r="E19" s="89" t="str">
         <f>IFERROR(VLOOKUP(B19,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="84"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="91"/>
       <c r="I19" s="41">
         <v>86</v>
       </c>
       <c r="J19" s="34">
         <v>0.52300000000000002</v>
       </c>
-      <c r="K19" s="157" t="s">
+      <c r="K19" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="L19" s="158"/>
-      <c r="M19" s="159"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="81"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="185"/>
+      <c r="N19" s="183"/>
+      <c r="O19" s="184"/>
+      <c r="P19" s="186"/>
       <c r="Q19" s="18"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
@@ -3512,24 +3512,24 @@
       <c r="D20" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="82" t="str">
+      <c r="E20" s="89" t="str">
         <f>IFERROR(VLOOKUP(B20,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="84"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="91"/>
       <c r="I20" s="41">
         <v>87</v>
       </c>
       <c r="J20" s="34">
         <v>0.52700000000000002</v>
       </c>
-      <c r="K20" s="157" t="s">
+      <c r="K20" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="L20" s="158"/>
-      <c r="M20" s="158"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
       <c r="N20" s="32"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -3547,24 +3547,24 @@
       <c r="D21" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="82" t="str">
+      <c r="E21" s="89" t="str">
         <f>IFERROR(VLOOKUP(B21,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="84"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
       <c r="I21" s="41">
         <v>24</v>
       </c>
       <c r="J21" s="34">
         <v>0.52700000000000002</v>
       </c>
-      <c r="K21" s="157" t="s">
+      <c r="K21" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="L21" s="158"/>
-      <c r="M21" s="158"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
       <c r="N21" s="32"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
@@ -3582,24 +3582,24 @@
       <c r="D22" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="82" t="str">
+      <c r="E22" s="89" t="str">
         <f>IFERROR(VLOOKUP(B22,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F22" s="83"/>
-      <c r="G22" s="83"/>
-      <c r="H22" s="84"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="91"/>
       <c r="I22" s="41">
         <v>48</v>
       </c>
       <c r="J22" s="34">
         <v>0.52700000000000002</v>
       </c>
-      <c r="K22" s="157" t="s">
+      <c r="K22" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="L22" s="158"/>
-      <c r="M22" s="158"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="51"/>
       <c r="N22" s="32"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -3611,15 +3611,15 @@
       <c r="B23" s="6"/>
       <c r="C23" s="49"/>
       <c r="D23" s="36"/>
-      <c r="E23" s="82"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="84"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="91"/>
       <c r="I23" s="41"/>
       <c r="J23" s="34"/>
-      <c r="K23" s="157"/>
-      <c r="L23" s="158"/>
-      <c r="M23" s="158"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="51"/>
       <c r="N23" s="32"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -3628,21 +3628,21 @@
       <c r="S23" s="1"/>
     </row>
     <row r="24" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="69"/>
-      <c r="C24" s="71"/>
+      <c r="B24" s="170"/>
+      <c r="C24" s="173"/>
       <c r="D24" s="36"/>
-      <c r="E24" s="82" t="str">
+      <c r="E24" s="89" t="str">
         <f>IFERROR(VLOOKUP(B24,'base itens'!A:B,2,0),"")</f>
         <v/>
       </c>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="84"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="91"/>
       <c r="I24" s="41"/>
       <c r="J24" s="34"/>
-      <c r="K24" s="157"/>
-      <c r="L24" s="158"/>
-      <c r="M24" s="158"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="51"/>
       <c r="N24" s="32"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -3651,18 +3651,18 @@
       <c r="S24" s="1"/>
     </row>
     <row r="25" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="69"/>
-      <c r="C25" s="71"/>
+      <c r="B25" s="170"/>
+      <c r="C25" s="173"/>
       <c r="D25" s="36"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="155"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="156"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="63"/>
       <c r="I25" s="43"/>
       <c r="J25" s="34"/>
-      <c r="K25" s="157"/>
-      <c r="L25" s="158"/>
-      <c r="M25" s="158"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="51"/>
+      <c r="M25" s="51"/>
       <c r="N25" s="32"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -3671,266 +3671,269 @@
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="2:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="70" t="str">
+      <c r="B26" s="171" t="str">
         <f>IF(B15&gt;0,B15,"")</f>
         <v/>
       </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="147"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148"/>
-      <c r="H26" s="149"/>
-      <c r="I26" s="7"/>
+      <c r="C26" s="174"/>
+      <c r="D26" s="169"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="7" t="str">
+        <f t="shared" ref="I26" si="1">IF(J15&gt;0,J15,"")</f>
+        <v/>
+      </c>
       <c r="J26" s="33"/>
-      <c r="K26" s="175"/>
-      <c r="L26" s="176"/>
-      <c r="M26" s="176"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="74"/>
       <c r="N26" s="47"/>
     </row>
     <row r="27" spans="2:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="150" t="s">
+      <c r="B27" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="151"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="152"/>
-      <c r="I27" s="152"/>
-      <c r="J27" s="152"/>
-      <c r="K27" s="152"/>
-      <c r="L27" s="152"/>
-      <c r="M27" s="152"/>
-      <c r="N27" s="153"/>
+      <c r="C27" s="172"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="87"/>
+      <c r="H27" s="87"/>
+      <c r="I27" s="87"/>
+      <c r="J27" s="87"/>
+      <c r="K27" s="87"/>
+      <c r="L27" s="87"/>
+      <c r="M27" s="87"/>
+      <c r="N27" s="88"/>
     </row>
     <row r="28" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="160" t="s">
+      <c r="B28" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="161"/>
-      <c r="D28" s="161"/>
-      <c r="E28" s="162"/>
-      <c r="F28" s="160" t="s">
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="161"/>
-      <c r="H28" s="161"/>
-      <c r="I28" s="161"/>
-      <c r="J28" s="162"/>
-      <c r="K28" s="160" t="s">
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="77"/>
+      <c r="K28" s="75" t="s">
         <v>149</v>
       </c>
-      <c r="L28" s="161"/>
-      <c r="M28" s="161"/>
-      <c r="N28" s="162"/>
+      <c r="L28" s="76"/>
+      <c r="M28" s="76"/>
+      <c r="N28" s="77"/>
     </row>
     <row r="29" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="163" t="s">
+      <c r="C29" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="D29" s="164"/>
-      <c r="E29" s="165"/>
-      <c r="F29" s="166" t="s">
+      <c r="D29" s="82"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="164"/>
-      <c r="H29" s="167"/>
-      <c r="I29" s="163" t="s">
+      <c r="G29" s="82"/>
+      <c r="H29" s="79"/>
+      <c r="I29" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="165"/>
-      <c r="K29" s="166" t="s">
+      <c r="J29" s="81"/>
+      <c r="K29" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="L29" s="167"/>
-      <c r="M29" s="163" t="s">
+      <c r="L29" s="79"/>
+      <c r="M29" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="N29" s="165"/>
+      <c r="N29" s="81"/>
     </row>
     <row r="30" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="168" t="s">
+      <c r="C30" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="169"/>
-      <c r="E30" s="170"/>
-      <c r="F30" s="171" t="s">
+      <c r="D30" s="56"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="169"/>
-      <c r="H30" s="172"/>
-      <c r="I30" s="173" t="s">
+      <c r="G30" s="56"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="J30" s="174"/>
-      <c r="K30" s="171" t="s">
+      <c r="J30" s="54"/>
+      <c r="K30" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="L30" s="172"/>
-      <c r="M30" s="173" t="s">
+      <c r="L30" s="57"/>
+      <c r="M30" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="N30" s="174"/>
+      <c r="N30" s="54"/>
     </row>
     <row r="31" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="37"/>
-      <c r="C31" s="168"/>
-      <c r="D31" s="169"/>
-      <c r="E31" s="170"/>
-      <c r="F31" s="171"/>
-      <c r="G31" s="169"/>
-      <c r="H31" s="172"/>
-      <c r="I31" s="173"/>
-      <c r="J31" s="174"/>
-      <c r="K31" s="171"/>
-      <c r="L31" s="172"/>
-      <c r="M31" s="173"/>
-      <c r="N31" s="174"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="54"/>
     </row>
     <row r="32" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="37"/>
-      <c r="C32" s="168"/>
-      <c r="D32" s="169"/>
-      <c r="E32" s="170"/>
-      <c r="F32" s="171"/>
-      <c r="G32" s="169"/>
-      <c r="H32" s="172"/>
-      <c r="I32" s="173"/>
-      <c r="J32" s="174"/>
-      <c r="K32" s="171"/>
-      <c r="L32" s="172"/>
-      <c r="M32" s="173"/>
-      <c r="N32" s="174"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="57"/>
+      <c r="M32" s="53"/>
+      <c r="N32" s="54"/>
     </row>
     <row r="33" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="37"/>
-      <c r="C33" s="168"/>
-      <c r="D33" s="169"/>
-      <c r="E33" s="170"/>
-      <c r="F33" s="171"/>
-      <c r="G33" s="169"/>
-      <c r="H33" s="172"/>
-      <c r="I33" s="173"/>
-      <c r="J33" s="174"/>
-      <c r="K33" s="171"/>
-      <c r="L33" s="172"/>
-      <c r="M33" s="173"/>
-      <c r="N33" s="174"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="54"/>
     </row>
     <row r="34" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="37"/>
-      <c r="C34" s="168"/>
-      <c r="D34" s="169"/>
-      <c r="E34" s="170"/>
-      <c r="F34" s="171"/>
-      <c r="G34" s="169"/>
-      <c r="H34" s="172"/>
-      <c r="I34" s="173"/>
-      <c r="J34" s="174"/>
-      <c r="K34" s="171"/>
-      <c r="L34" s="172"/>
-      <c r="M34" s="173"/>
-      <c r="N34" s="174"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="55"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="54"/>
     </row>
     <row r="35" spans="2:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="38"/>
-      <c r="C35" s="168"/>
-      <c r="D35" s="169"/>
-      <c r="E35" s="170"/>
-      <c r="F35" s="171"/>
-      <c r="G35" s="169"/>
-      <c r="H35" s="172"/>
-      <c r="I35" s="173"/>
-      <c r="J35" s="174"/>
-      <c r="K35" s="171"/>
-      <c r="L35" s="172"/>
-      <c r="M35" s="173"/>
-      <c r="N35" s="174"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="54"/>
     </row>
     <row r="36" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="183" t="s">
+      <c r="B36" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="184"/>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
-      <c r="F36" s="184"/>
-      <c r="G36" s="184"/>
-      <c r="H36" s="184"/>
-      <c r="I36" s="184"/>
-      <c r="J36" s="184"/>
-      <c r="K36" s="184"/>
-      <c r="L36" s="184"/>
-      <c r="M36" s="184"/>
-      <c r="N36" s="185"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="71"/>
+      <c r="M36" s="71"/>
+      <c r="N36" s="72"/>
       <c r="S36" s="8"/>
     </row>
     <row r="37" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="54" t="s">
+      <c r="B37" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="55" t="s">
+      <c r="C37" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="55" t="s">
+      <c r="D37" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="E37" s="182" t="s">
+      <c r="E37" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="182"/>
-      <c r="G37" s="182"/>
-      <c r="H37" s="182"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
       <c r="I37" s="27" t="s">
         <v>73</v>
       </c>
       <c r="J37" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="K37" s="127" t="s">
+      <c r="K37" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="L37" s="128"/>
-      <c r="M37" s="128"/>
-      <c r="N37" s="181"/>
+      <c r="L37" s="67"/>
+      <c r="M37" s="67"/>
+      <c r="N37" s="68"/>
       <c r="S37" s="8"/>
     </row>
     <row r="38" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="51">
+      <c r="C38" s="125">
         <v>46314</v>
       </c>
-      <c r="D38" s="53" t="s">
+      <c r="D38" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="180" t="s">
+      <c r="E38" s="128" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="180"/>
-      <c r="G38" s="180"/>
-      <c r="H38" s="180"/>
+      <c r="F38" s="128"/>
+      <c r="G38" s="128"/>
+      <c r="H38" s="128"/>
       <c r="I38" s="29">
         <v>0</v>
       </c>
       <c r="J38" s="29">
         <v>0</v>
       </c>
-      <c r="K38" s="177" t="s">
+      <c r="K38" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="L38" s="178"/>
-      <c r="M38" s="178"/>
-      <c r="N38" s="179"/>
+      <c r="L38" s="59"/>
+      <c r="M38" s="59"/>
+      <c r="N38" s="60"/>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
       <c r="Q38" s="19"/>
@@ -3941,30 +3944,30 @@
       <c r="B39" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="51">
+      <c r="C39" s="125">
         <v>46314</v>
       </c>
-      <c r="D39" s="53" t="s">
+      <c r="D39" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="180" t="s">
+      <c r="E39" s="128" t="s">
         <v>70</v>
       </c>
-      <c r="F39" s="180"/>
-      <c r="G39" s="180"/>
-      <c r="H39" s="180"/>
+      <c r="F39" s="128"/>
+      <c r="G39" s="128"/>
+      <c r="H39" s="128"/>
       <c r="I39" s="29">
         <v>0</v>
       </c>
       <c r="J39" s="29">
         <v>0</v>
       </c>
-      <c r="K39" s="177" t="s">
+      <c r="K39" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="L39" s="178"/>
-      <c r="M39" s="178"/>
-      <c r="N39" s="179"/>
+      <c r="L39" s="59"/>
+      <c r="M39" s="59"/>
+      <c r="N39" s="60"/>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
       <c r="Q39" s="19"/>
@@ -3975,30 +3978,30 @@
       <c r="B40" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="51">
+      <c r="C40" s="125">
         <v>46314</v>
       </c>
-      <c r="D40" s="53" t="s">
+      <c r="D40" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="E40" s="180" t="s">
+      <c r="E40" s="128" t="s">
         <v>70</v>
       </c>
-      <c r="F40" s="180"/>
-      <c r="G40" s="180"/>
-      <c r="H40" s="180"/>
+      <c r="F40" s="128"/>
+      <c r="G40" s="128"/>
+      <c r="H40" s="128"/>
       <c r="I40" s="29">
         <v>0</v>
       </c>
       <c r="J40" s="29">
         <v>0</v>
       </c>
-      <c r="K40" s="177" t="s">
+      <c r="K40" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="L40" s="178"/>
-      <c r="M40" s="178"/>
-      <c r="N40" s="179"/>
+      <c r="L40" s="59"/>
+      <c r="M40" s="59"/>
+      <c r="N40" s="60"/>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
       <c r="Q40" s="19"/>
@@ -4007,18 +4010,18 @@
     </row>
     <row r="41" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="7"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="180"/>
-      <c r="F41" s="180"/>
-      <c r="G41" s="180"/>
-      <c r="H41" s="180"/>
+      <c r="C41" s="126"/>
+      <c r="D41" s="127"/>
+      <c r="E41" s="128"/>
+      <c r="F41" s="128"/>
+      <c r="G41" s="128"/>
+      <c r="H41" s="128"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
-      <c r="K41" s="177"/>
-      <c r="L41" s="178"/>
-      <c r="M41" s="178"/>
-      <c r="N41" s="179"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="59"/>
+      <c r="M41" s="59"/>
+      <c r="N41" s="60"/>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
       <c r="Q41" s="19"/>
@@ -4026,21 +4029,21 @@
       <c r="S41" s="8"/>
     </row>
     <row r="42" spans="2:19" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="B42" s="93" t="s">
+      <c r="B42" s="122" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="94"/>
-      <c r="D42" s="94"/>
-      <c r="E42" s="94"/>
-      <c r="F42" s="94"/>
-      <c r="G42" s="94"/>
-      <c r="H42" s="94"/>
-      <c r="I42" s="95"/>
-      <c r="J42" s="96"/>
-      <c r="K42" s="94"/>
-      <c r="L42" s="94"/>
-      <c r="M42" s="94"/>
-      <c r="N42" s="97"/>
+      <c r="C42" s="123"/>
+      <c r="D42" s="123"/>
+      <c r="E42" s="123"/>
+      <c r="F42" s="123"/>
+      <c r="G42" s="123"/>
+      <c r="H42" s="123"/>
+      <c r="I42" s="124"/>
+      <c r="J42" s="131"/>
+      <c r="K42" s="123"/>
+      <c r="L42" s="123"/>
+      <c r="M42" s="123"/>
+      <c r="N42" s="132"/>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
       <c r="Q42" s="19"/>
@@ -4057,20 +4060,20 @@
       <c r="D43" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="E43" s="186" t="s">
+      <c r="E43" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="F43" s="186"/>
-      <c r="G43" s="186"/>
-      <c r="H43" s="186"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="52"/>
       <c r="I43" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="J43" s="90"/>
-      <c r="K43" s="91"/>
-      <c r="L43" s="91"/>
-      <c r="M43" s="91"/>
-      <c r="N43" s="92"/>
+      <c r="J43" s="115"/>
+      <c r="K43" s="116"/>
+      <c r="L43" s="116"/>
+      <c r="M43" s="116"/>
+      <c r="N43" s="117"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="17"/>
@@ -4081,26 +4084,26 @@
       <c r="B44" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="51">
+      <c r="C44" s="125">
         <v>46314</v>
       </c>
-      <c r="D44" s="53" t="s">
+      <c r="D44" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="180" t="s">
+      <c r="E44" s="128" t="s">
         <v>70</v>
       </c>
-      <c r="F44" s="180"/>
-      <c r="G44" s="180"/>
-      <c r="H44" s="180"/>
+      <c r="F44" s="128"/>
+      <c r="G44" s="128"/>
+      <c r="H44" s="128"/>
       <c r="I44" s="29">
         <v>1137</v>
       </c>
-      <c r="J44" s="86"/>
-      <c r="K44" s="87"/>
-      <c r="L44" s="87"/>
-      <c r="M44" s="87"/>
-      <c r="N44" s="87"/>
+      <c r="J44" s="118"/>
+      <c r="K44" s="119"/>
+      <c r="L44" s="119"/>
+      <c r="M44" s="119"/>
+      <c r="N44" s="119"/>
       <c r="O44" s="48">
         <v>14003101001</v>
       </c>
@@ -4117,26 +4120,26 @@
       <c r="B45" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="51">
+      <c r="C45" s="125">
         <v>46314</v>
       </c>
-      <c r="D45" s="53" t="s">
+      <c r="D45" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="180" t="s">
+      <c r="E45" s="128" t="s">
         <v>70</v>
       </c>
-      <c r="F45" s="180"/>
-      <c r="G45" s="180"/>
-      <c r="H45" s="180"/>
+      <c r="F45" s="128"/>
+      <c r="G45" s="128"/>
+      <c r="H45" s="128"/>
       <c r="I45" s="29">
         <v>1417.5</v>
       </c>
-      <c r="J45" s="88"/>
-      <c r="K45" s="89"/>
-      <c r="L45" s="89"/>
-      <c r="M45" s="89"/>
-      <c r="N45" s="89"/>
+      <c r="J45" s="120"/>
+      <c r="K45" s="121"/>
+      <c r="L45" s="121"/>
+      <c r="M45" s="121"/>
+      <c r="N45" s="121"/>
       <c r="O45" s="7">
         <v>14003201001</v>
       </c>
@@ -4153,26 +4156,26 @@
       <c r="B46" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="51">
+      <c r="C46" s="125">
         <v>46314</v>
       </c>
-      <c r="D46" s="53" t="s">
+      <c r="D46" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="E46" s="180" t="s">
+      <c r="E46" s="128" t="s">
         <v>70</v>
       </c>
-      <c r="F46" s="180"/>
-      <c r="G46" s="180"/>
-      <c r="H46" s="180"/>
+      <c r="F46" s="128"/>
+      <c r="G46" s="128"/>
+      <c r="H46" s="128"/>
       <c r="I46" s="29">
         <v>454</v>
       </c>
-      <c r="J46" s="88"/>
-      <c r="K46" s="89"/>
-      <c r="L46" s="89"/>
-      <c r="M46" s="89"/>
-      <c r="N46" s="89"/>
+      <c r="J46" s="120"/>
+      <c r="K46" s="121"/>
+      <c r="L46" s="121"/>
+      <c r="M46" s="121"/>
+      <c r="N46" s="121"/>
       <c r="O46" s="7">
         <v>13978401001</v>
       </c>
@@ -4189,60 +4192,60 @@
       <c r="B47" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="51">
+      <c r="C47" s="125">
         <v>46314</v>
       </c>
-      <c r="D47" s="53" t="s">
+      <c r="D47" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="180" t="s">
+      <c r="E47" s="128" t="s">
         <v>70</v>
       </c>
-      <c r="F47" s="180"/>
-      <c r="G47" s="180"/>
-      <c r="H47" s="180"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="128"/>
       <c r="I47" s="29">
         <v>1098</v>
       </c>
-      <c r="J47" s="88"/>
-      <c r="K47" s="89"/>
-      <c r="L47" s="89"/>
-      <c r="M47" s="89"/>
-      <c r="N47" s="89"/>
+      <c r="J47" s="120"/>
+      <c r="K47" s="121"/>
+      <c r="L47" s="121"/>
+      <c r="M47" s="121"/>
+      <c r="N47" s="121"/>
       <c r="O47" s="4"/>
     </row>
     <row r="48" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B48" s="7"/>
-      <c r="C48" s="51"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="180"/>
-      <c r="F48" s="180"/>
-      <c r="G48" s="180"/>
-      <c r="H48" s="180"/>
+      <c r="C48" s="125"/>
+      <c r="D48" s="127"/>
+      <c r="E48" s="128"/>
+      <c r="F48" s="128"/>
+      <c r="G48" s="128"/>
+      <c r="H48" s="128"/>
       <c r="I48" s="29"/>
-      <c r="J48" s="88"/>
-      <c r="K48" s="89"/>
-      <c r="L48" s="89"/>
-      <c r="M48" s="89"/>
-      <c r="N48" s="89"/>
+      <c r="J48" s="120"/>
+      <c r="K48" s="121"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
       <c r="O48" s="4">
         <v>13851401001</v>
       </c>
     </row>
     <row r="49" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B49" s="51"/>
-      <c r="C49" s="52"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="117"/>
-      <c r="F49" s="117"/>
-      <c r="G49" s="117"/>
-      <c r="H49" s="117"/>
+      <c r="B49" s="125"/>
+      <c r="C49" s="126"/>
+      <c r="D49" s="127"/>
+      <c r="E49" s="92"/>
+      <c r="F49" s="92"/>
+      <c r="G49" s="92"/>
+      <c r="H49" s="92"/>
       <c r="I49" s="29"/>
-      <c r="J49" s="88"/>
-      <c r="K49" s="89"/>
-      <c r="L49" s="89"/>
-      <c r="M49" s="89"/>
-      <c r="N49" s="89"/>
+      <c r="J49" s="120"/>
+      <c r="K49" s="121"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121"/>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.3"/>
     <row r="51" spans="2:14" x14ac:dyDescent="0.3"/>
@@ -4340,83 +4343,6 @@
     <row r="143" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K41:N41"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="K37:N37"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="B36:N36"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:J28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="N7:Q7"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="B27:N27"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K26:M26"/>
     <mergeCell ref="E11:H11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="J44:N49"/>
@@ -4441,6 +4367,83 @@
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="B27:N27"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:J28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="B36:N36"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K41:N41"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="2">
@@ -7162,23 +7165,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="86c6d835-384d-4eee-b5e4-7a7d42cb3d19" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004A4A59D84FFE1748BB38BBBF60A87067" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="122dd576e940e33e9bdee9d882a1d0b8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="86c6d835-384d-4eee-b5e4-7a7d42cb3d19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ef1bdbddccf683fbaa0b0495f4025495" ns3:_="">
     <xsd:import namespace="86c6d835-384d-4eee-b5e4-7a7d42cb3d19"/>
@@ -7334,31 +7320,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54BB2CB7-F996-4C7B-B8F6-D759D6846113}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="86c6d835-384d-4eee-b5e4-7a7d42cb3d19"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{601125AE-989D-4A8E-B764-68DA4A2ACCDA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="86c6d835-384d-4eee-b5e4-7a7d42cb3d19" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A98C6C55-1841-4DCB-B412-B1F89DBD7BD9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7374,4 +7353,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{601125AE-989D-4A8E-B764-68DA4A2ACCDA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54BB2CB7-F996-4C7B-B8F6-D759D6846113}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="86c6d835-384d-4eee-b5e4-7a7d42cb3d19"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/api/_modelo_report.xlsx
+++ b/api/_modelo_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego.batista\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego.batista\Downloads\masseiras-app-main\masseiras-app-main\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C774446-84B2-4753-AB52-5C4FFD3205C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EFB7B2-E71C-43F5-BEFF-E2C4D597E8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" xr2:uid="{A61D48FF-59C3-42AE-88A3-50A1935DB5F5}"/>
   </bookViews>
@@ -1970,17 +1970,494 @@
     <xf numFmtId="14" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="38" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="9" fontId="6" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="9"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="9"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="9"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -1990,17 +2467,13 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2014,32 +2487,8 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2062,457 +2511,8 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="9"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="9"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="9"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="5" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="38" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -2946,28 +2946,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="114"/>
+      <c r="B1" s="85"/>
     </row>
     <row r="2" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="114"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="102" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="104"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="131"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="132"/>
       <c r="P2" s="17" t="s">
         <v>3</v>
       </c>
@@ -2977,21 +2977,21 @@
       <c r="R2" s="17"/>
     </row>
     <row r="3" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="125" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="107"/>
+      <c r="C3" s="133"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="134"/>
+      <c r="M3" s="134"/>
+      <c r="N3" s="135"/>
       <c r="O3" s="3"/>
       <c r="P3" s="17" t="s">
         <v>4</v>
@@ -3002,19 +3002,19 @@
       <c r="R3" s="17"/>
     </row>
     <row r="4" spans="1:19" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="100"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="109"/>
-      <c r="L4" s="109"/>
-      <c r="M4" s="109"/>
-      <c r="N4" s="110"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137"/>
+      <c r="M4" s="137"/>
+      <c r="N4" s="138"/>
       <c r="O4" s="3"/>
       <c r="P4" s="17" t="s">
         <v>11</v>
@@ -3031,15 +3031,15 @@
       <c r="C5" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="166" t="s">
+      <c r="D5" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="111" t="s">
+      <c r="E5" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="112"/>
-      <c r="G5" s="112"/>
-      <c r="H5" s="113"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="141"/>
       <c r="I5" s="21" t="s">
         <v>35</v>
       </c>
@@ -3072,16 +3072,16 @@
       <c r="C6" s="49">
         <v>46314</v>
       </c>
-      <c r="D6" s="168" t="s">
+      <c r="D6" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="89" t="str">
+      <c r="E6" s="82" t="str">
         <f>IFERROR(VLOOKUP(B6,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="91"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="84"/>
       <c r="I6" s="7">
         <v>66</v>
       </c>
@@ -3092,16 +3092,16 @@
         <f>J6/I6</f>
         <v>1.303030303030303</v>
       </c>
-      <c r="L6" s="162">
+      <c r="L6" s="64">
         <v>4650</v>
       </c>
-      <c r="M6" s="175">
+      <c r="M6" s="73">
         <v>14632901001</v>
       </c>
-      <c r="N6" s="176"/>
-      <c r="O6" s="177"/>
-      <c r="P6" s="177"/>
-      <c r="Q6" s="177"/>
+      <c r="N6" s="145"/>
+      <c r="O6" s="146"/>
+      <c r="P6" s="146"/>
+      <c r="Q6" s="146"/>
       <c r="R6" s="17"/>
       <c r="S6" s="1"/>
     </row>
@@ -3115,13 +3115,13 @@
       <c r="D7" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="89" t="str">
+      <c r="E7" s="82" t="str">
         <f>IFERROR(VLOOKUP(B7,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F7" s="90"/>
-      <c r="G7" s="90"/>
-      <c r="H7" s="91"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="84"/>
       <c r="I7" s="7">
         <v>86</v>
       </c>
@@ -3132,16 +3132,16 @@
         <f>J7/I7</f>
         <v>1.0116279069767442</v>
       </c>
-      <c r="L7" s="162">
+      <c r="L7" s="64">
         <v>5400</v>
       </c>
-      <c r="M7" s="175">
+      <c r="M7" s="73">
         <v>14632601001</v>
       </c>
-      <c r="N7" s="176"/>
-      <c r="O7" s="177"/>
-      <c r="P7" s="177"/>
-      <c r="Q7" s="177"/>
+      <c r="N7" s="145"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="146"/>
+      <c r="Q7" s="146"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
@@ -3155,13 +3155,13 @@
       <c r="D8" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="89" t="str">
+      <c r="E8" s="82" t="str">
         <f>IFERROR(VLOOKUP(B8,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="91"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="84"/>
       <c r="I8" s="11">
         <v>13</v>
       </c>
@@ -3172,16 +3172,16 @@
         <f>J8/I8</f>
         <v>1.8461538461538463</v>
       </c>
-      <c r="L8" s="162">
+      <c r="L8" s="64">
         <v>780</v>
       </c>
-      <c r="M8" s="175">
+      <c r="M8" s="73">
         <v>14632801001</v>
       </c>
-      <c r="N8" s="178"/>
-      <c r="O8" s="179"/>
-      <c r="P8" s="179"/>
-      <c r="Q8" s="179"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="75"/>
+      <c r="P8" s="75"/>
+      <c r="Q8" s="75"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
@@ -3195,13 +3195,13 @@
       <c r="D9" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="89" t="str">
+      <c r="E9" s="82" t="str">
         <f>IFERROR(VLOOKUP(B9,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="91"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="84"/>
       <c r="I9" s="7">
         <v>61</v>
       </c>
@@ -3215,29 +3215,29 @@
       <c r="L9" s="24">
         <v>3720</v>
       </c>
-      <c r="M9" s="133">
+      <c r="M9" s="56">
         <v>14632701001</v>
       </c>
-      <c r="N9" s="180" t="s">
+      <c r="N9" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="O9" s="181"/>
-      <c r="P9" s="181"/>
-      <c r="Q9" s="182"/>
+      <c r="O9" s="77"/>
+      <c r="P9" s="77"/>
+      <c r="Q9" s="78"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
-      <c r="C10" s="165"/>
+      <c r="C10" s="65"/>
       <c r="D10" s="36"/>
-      <c r="E10" s="89" t="str">
+      <c r="E10" s="82" t="str">
         <f>IFERROR(VLOOKUP(B10,'base itens'!A:B,2,0),"")</f>
         <v/>
       </c>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="91"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="84"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="16" t="e">
@@ -3245,112 +3245,112 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L10" s="24"/>
-      <c r="M10" s="133"/>
-      <c r="N10" s="180"/>
-      <c r="O10" s="181"/>
-      <c r="P10" s="181"/>
-      <c r="Q10" s="182"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="76"/>
+      <c r="O10" s="77"/>
+      <c r="P10" s="77"/>
+      <c r="Q10" s="78"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="134"/>
-      <c r="C11" s="165"/>
-      <c r="D11" s="169"/>
-      <c r="E11" s="89" t="str">
+      <c r="B11" s="57"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="82" t="str">
         <f>IFERROR(VLOOKUP(B11,'base itens'!A:B,2,0),"")</f>
         <v/>
       </c>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="135"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
       <c r="K11" s="16" t="e">
-        <f t="shared" ref="K10:K11" si="0">J11/I11</f>
+        <f t="shared" ref="K11" si="0">J11/I11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L11" s="136"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="180"/>
-      <c r="O11" s="181"/>
-      <c r="P11" s="181"/>
-      <c r="Q11" s="182"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="76"/>
+      <c r="O11" s="77"/>
+      <c r="P11" s="77"/>
+      <c r="Q11" s="78"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="143" t="s">
+      <c r="B12" s="98" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="143"/>
-      <c r="D12" s="167"/>
-      <c r="E12" s="143"/>
-      <c r="F12" s="143"/>
-      <c r="G12" s="143"/>
-      <c r="H12" s="143"/>
-      <c r="I12" s="143"/>
-      <c r="J12" s="143"/>
-      <c r="K12" s="143"/>
-      <c r="L12" s="143"/>
-      <c r="M12" s="143"/>
-      <c r="N12" s="167"/>
-      <c r="O12" s="167"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="98"/>
+      <c r="N12" s="99"/>
+      <c r="O12" s="99"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="18"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="146"/>
-      <c r="C13" s="164"/>
-      <c r="D13" s="144" t="s">
+      <c r="B13" s="100"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="149" t="s">
+      <c r="E13" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="149"/>
-      <c r="G13" s="149"/>
-      <c r="H13" s="150"/>
-      <c r="I13" s="145" t="s">
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="63" t="s">
         <v>151</v>
       </c>
-      <c r="J13" s="145" t="s">
+      <c r="J13" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="K13" s="161"/>
-      <c r="L13" s="149"/>
-      <c r="M13" s="149"/>
-      <c r="N13" s="149"/>
-      <c r="O13" s="144"/>
+      <c r="K13" s="107"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="105"/>
+      <c r="N13" s="105"/>
+      <c r="O13" s="62"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="18"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="147"/>
-      <c r="C14" s="151"/>
-      <c r="D14" s="168" t="s">
+      <c r="B14" s="101"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="138" t="s">
+      <c r="E14" s="142" t="s">
         <v>104</v>
       </c>
-      <c r="F14" s="139"/>
-      <c r="G14" s="139"/>
-      <c r="H14" s="140"/>
-      <c r="I14" s="141">
+      <c r="F14" s="143"/>
+      <c r="G14" s="143"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="60">
         <v>285</v>
       </c>
       <c r="J14" s="12"/>
-      <c r="K14" s="142" t="s">
+      <c r="K14" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="L14" s="152"/>
-      <c r="M14" s="153"/>
-      <c r="N14" s="154"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="109"/>
+      <c r="N14" s="110"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="18"/>
@@ -3358,27 +3358,27 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="147"/>
-      <c r="C15" s="151"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="104"/>
       <c r="D15" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="92" t="s">
+      <c r="E15" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="92"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
       <c r="I15" s="7">
         <v>168</v>
       </c>
       <c r="J15" s="7"/>
-      <c r="K15" s="142" t="s">
+      <c r="K15" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="L15" s="155"/>
-      <c r="M15" s="156"/>
-      <c r="N15" s="157"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="113"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="18"/>
@@ -3386,27 +3386,27 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19" s="5" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="148"/>
-      <c r="C16" s="151"/>
-      <c r="D16" s="169" t="s">
+      <c r="B16" s="102"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="92" t="s">
+      <c r="E16" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="92"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="92"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="117"/>
       <c r="I16" s="7">
         <v>282</v>
       </c>
       <c r="J16" s="7"/>
-      <c r="K16" s="142" t="s">
+      <c r="K16" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="L16" s="158"/>
-      <c r="M16" s="159"/>
-      <c r="N16" s="160"/>
+      <c r="L16" s="114"/>
+      <c r="M16" s="115"/>
+      <c r="N16" s="116"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="18"/>
@@ -3414,21 +3414,21 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="93" t="s">
+      <c r="B17" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="163"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="94"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="94"/>
-      <c r="N17" s="95"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="120"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="121"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="18"/>
@@ -3440,27 +3440,27 @@
         <v>5</v>
       </c>
       <c r="C18" s="31"/>
-      <c r="D18" s="130" t="s">
+      <c r="D18" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="E18" s="66" t="s">
+      <c r="E18" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
-      <c r="H18" s="101"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="128"/>
+      <c r="H18" s="129"/>
       <c r="I18" s="31" t="s">
         <v>41</v>
       </c>
       <c r="J18" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="K18" s="96" t="s">
+      <c r="K18" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="L18" s="97"/>
-      <c r="M18" s="97"/>
-      <c r="N18" s="98"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="123"/>
+      <c r="N18" s="124"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="18"/>
@@ -3474,30 +3474,30 @@
       <c r="C19" s="49">
         <v>46314</v>
       </c>
-      <c r="D19" s="168" t="s">
+      <c r="D19" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="89" t="str">
+      <c r="E19" s="82" t="str">
         <f>IFERROR(VLOOKUP(B19,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="91"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="84"/>
       <c r="I19" s="41">
         <v>86</v>
       </c>
       <c r="J19" s="34">
         <v>0.52300000000000002</v>
       </c>
-      <c r="K19" s="50" t="s">
+      <c r="K19" s="157" t="s">
         <v>142</v>
       </c>
-      <c r="L19" s="51"/>
-      <c r="M19" s="185"/>
-      <c r="N19" s="183"/>
-      <c r="O19" s="184"/>
-      <c r="P19" s="186"/>
+      <c r="L19" s="158"/>
+      <c r="M19" s="159"/>
+      <c r="N19" s="79"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="81"/>
       <c r="Q19" s="18"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
@@ -3512,24 +3512,24 @@
       <c r="D20" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="89" t="str">
+      <c r="E20" s="82" t="str">
         <f>IFERROR(VLOOKUP(B20,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="91"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="84"/>
       <c r="I20" s="41">
         <v>87</v>
       </c>
       <c r="J20" s="34">
         <v>0.52700000000000002</v>
       </c>
-      <c r="K20" s="50" t="s">
+      <c r="K20" s="157" t="s">
         <v>142</v>
       </c>
-      <c r="L20" s="51"/>
-      <c r="M20" s="51"/>
+      <c r="L20" s="158"/>
+      <c r="M20" s="158"/>
       <c r="N20" s="32"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -3547,24 +3547,24 @@
       <c r="D21" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="89" t="str">
+      <c r="E21" s="82" t="str">
         <f>IFERROR(VLOOKUP(B21,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H PCT C/ 7,5 KG</v>
       </c>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="91"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="84"/>
       <c r="I21" s="41">
         <v>24</v>
       </c>
       <c r="J21" s="34">
         <v>0.52700000000000002</v>
       </c>
-      <c r="K21" s="50" t="s">
+      <c r="K21" s="157" t="s">
         <v>142</v>
       </c>
-      <c r="L21" s="51"/>
-      <c r="M21" s="51"/>
+      <c r="L21" s="158"/>
+      <c r="M21" s="158"/>
       <c r="N21" s="32"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
@@ -3582,24 +3582,24 @@
       <c r="D22" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="89" t="str">
+      <c r="E22" s="82" t="str">
         <f>IFERROR(VLOOKUP(B22,'base itens'!A:B,2,0),"")</f>
         <v>PAO FRANCES 6 H (G) PCT C/ 7,5 KG    </v>
       </c>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="91"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="84"/>
       <c r="I22" s="41">
         <v>48</v>
       </c>
       <c r="J22" s="34">
         <v>0.52700000000000002</v>
       </c>
-      <c r="K22" s="50" t="s">
+      <c r="K22" s="157" t="s">
         <v>142</v>
       </c>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51"/>
+      <c r="L22" s="158"/>
+      <c r="M22" s="158"/>
       <c r="N22" s="32"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -3611,15 +3611,15 @@
       <c r="B23" s="6"/>
       <c r="C23" s="49"/>
       <c r="D23" s="36"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="91"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="84"/>
       <c r="I23" s="41"/>
       <c r="J23" s="34"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="51"/>
-      <c r="M23" s="51"/>
+      <c r="K23" s="157"/>
+      <c r="L23" s="158"/>
+      <c r="M23" s="158"/>
       <c r="N23" s="32"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -3628,21 +3628,21 @@
       <c r="S23" s="1"/>
     </row>
     <row r="24" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="170"/>
-      <c r="C24" s="173"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="71"/>
       <c r="D24" s="36"/>
-      <c r="E24" s="89" t="str">
+      <c r="E24" s="82" t="str">
         <f>IFERROR(VLOOKUP(B24,'base itens'!A:B,2,0),"")</f>
         <v/>
       </c>
-      <c r="F24" s="90"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="91"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="84"/>
       <c r="I24" s="41"/>
       <c r="J24" s="34"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
+      <c r="K24" s="157"/>
+      <c r="L24" s="158"/>
+      <c r="M24" s="158"/>
       <c r="N24" s="32"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -3651,18 +3651,18 @@
       <c r="S24" s="1"/>
     </row>
     <row r="25" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="170"/>
-      <c r="C25" s="173"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="71"/>
       <c r="D25" s="36"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="63"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="155"/>
+      <c r="G25" s="155"/>
+      <c r="H25" s="156"/>
       <c r="I25" s="43"/>
       <c r="J25" s="34"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="51"/>
-      <c r="M25" s="51"/>
+      <c r="K25" s="157"/>
+      <c r="L25" s="158"/>
+      <c r="M25" s="158"/>
       <c r="N25" s="32"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -3671,269 +3671,266 @@
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="2:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="171" t="str">
+      <c r="B26" s="70" t="str">
         <f>IF(B15&gt;0,B15,"")</f>
         <v/>
       </c>
-      <c r="C26" s="174"/>
-      <c r="D26" s="169"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="84"/>
-      <c r="G26" s="84"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="7" t="str">
-        <f t="shared" ref="I26" si="1">IF(J15&gt;0,J15,"")</f>
-        <v/>
-      </c>
+      <c r="C26" s="72"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="148"/>
+      <c r="G26" s="148"/>
+      <c r="H26" s="149"/>
+      <c r="I26" s="7"/>
       <c r="J26" s="33"/>
-      <c r="K26" s="73"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
+      <c r="K26" s="175"/>
+      <c r="L26" s="176"/>
+      <c r="M26" s="176"/>
       <c r="N26" s="47"/>
     </row>
     <row r="27" spans="2:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="86" t="s">
+      <c r="B27" s="150" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="172"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="87"/>
-      <c r="H27" s="87"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="87"/>
-      <c r="N27" s="88"/>
+      <c r="C27" s="151"/>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="152"/>
+      <c r="G27" s="152"/>
+      <c r="H27" s="152"/>
+      <c r="I27" s="152"/>
+      <c r="J27" s="152"/>
+      <c r="K27" s="152"/>
+      <c r="L27" s="152"/>
+      <c r="M27" s="152"/>
+      <c r="N27" s="153"/>
     </row>
     <row r="28" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="160" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="75" t="s">
+      <c r="C28" s="161"/>
+      <c r="D28" s="161"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="160" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="77"/>
-      <c r="K28" s="75" t="s">
+      <c r="G28" s="161"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="161"/>
+      <c r="J28" s="162"/>
+      <c r="K28" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="L28" s="76"/>
-      <c r="M28" s="76"/>
-      <c r="N28" s="77"/>
+      <c r="L28" s="161"/>
+      <c r="M28" s="161"/>
+      <c r="N28" s="162"/>
     </row>
     <row r="29" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="80" t="s">
+      <c r="C29" s="163" t="s">
         <v>15</v>
       </c>
-      <c r="D29" s="82"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="78" t="s">
+      <c r="D29" s="164"/>
+      <c r="E29" s="165"/>
+      <c r="F29" s="166" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="82"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="80" t="s">
+      <c r="G29" s="164"/>
+      <c r="H29" s="167"/>
+      <c r="I29" s="163" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="81"/>
-      <c r="K29" s="78" t="s">
+      <c r="J29" s="165"/>
+      <c r="K29" s="166" t="s">
         <v>69</v>
       </c>
-      <c r="L29" s="79"/>
-      <c r="M29" s="80" t="s">
+      <c r="L29" s="167"/>
+      <c r="M29" s="163" t="s">
         <v>15</v>
       </c>
-      <c r="N29" s="81"/>
+      <c r="N29" s="165"/>
     </row>
     <row r="30" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="64" t="s">
+      <c r="C30" s="168" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="56"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="55" t="s">
+      <c r="D30" s="169"/>
+      <c r="E30" s="170"/>
+      <c r="F30" s="171" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="56"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="53" t="s">
+      <c r="G30" s="169"/>
+      <c r="H30" s="172"/>
+      <c r="I30" s="173" t="s">
         <v>63</v>
       </c>
-      <c r="J30" s="54"/>
-      <c r="K30" s="55" t="s">
+      <c r="J30" s="174"/>
+      <c r="K30" s="171" t="s">
         <v>98</v>
       </c>
-      <c r="L30" s="57"/>
-      <c r="M30" s="53" t="s">
+      <c r="L30" s="172"/>
+      <c r="M30" s="173" t="s">
         <v>68</v>
       </c>
-      <c r="N30" s="54"/>
+      <c r="N30" s="174"/>
     </row>
     <row r="31" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="37"/>
-      <c r="C31" s="64"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="54"/>
+      <c r="C31" s="168"/>
+      <c r="D31" s="169"/>
+      <c r="E31" s="170"/>
+      <c r="F31" s="171"/>
+      <c r="G31" s="169"/>
+      <c r="H31" s="172"/>
+      <c r="I31" s="173"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="171"/>
+      <c r="L31" s="172"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="174"/>
     </row>
     <row r="32" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="37"/>
-      <c r="C32" s="64"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="55"/>
-      <c r="L32" s="57"/>
-      <c r="M32" s="53"/>
-      <c r="N32" s="54"/>
+      <c r="C32" s="168"/>
+      <c r="D32" s="169"/>
+      <c r="E32" s="170"/>
+      <c r="F32" s="171"/>
+      <c r="G32" s="169"/>
+      <c r="H32" s="172"/>
+      <c r="I32" s="173"/>
+      <c r="J32" s="174"/>
+      <c r="K32" s="171"/>
+      <c r="L32" s="172"/>
+      <c r="M32" s="173"/>
+      <c r="N32" s="174"/>
     </row>
     <row r="33" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="37"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="65"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="57"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="54"/>
+      <c r="C33" s="168"/>
+      <c r="D33" s="169"/>
+      <c r="E33" s="170"/>
+      <c r="F33" s="171"/>
+      <c r="G33" s="169"/>
+      <c r="H33" s="172"/>
+      <c r="I33" s="173"/>
+      <c r="J33" s="174"/>
+      <c r="K33" s="171"/>
+      <c r="L33" s="172"/>
+      <c r="M33" s="173"/>
+      <c r="N33" s="174"/>
     </row>
     <row r="34" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="37"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="54"/>
-      <c r="K34" s="55"/>
-      <c r="L34" s="57"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="54"/>
+      <c r="C34" s="168"/>
+      <c r="D34" s="169"/>
+      <c r="E34" s="170"/>
+      <c r="F34" s="171"/>
+      <c r="G34" s="169"/>
+      <c r="H34" s="172"/>
+      <c r="I34" s="173"/>
+      <c r="J34" s="174"/>
+      <c r="K34" s="171"/>
+      <c r="L34" s="172"/>
+      <c r="M34" s="173"/>
+      <c r="N34" s="174"/>
     </row>
     <row r="35" spans="2:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="38"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="54"/>
-      <c r="K35" s="55"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="54"/>
+      <c r="C35" s="168"/>
+      <c r="D35" s="169"/>
+      <c r="E35" s="170"/>
+      <c r="F35" s="171"/>
+      <c r="G35" s="169"/>
+      <c r="H35" s="172"/>
+      <c r="I35" s="173"/>
+      <c r="J35" s="174"/>
+      <c r="K35" s="171"/>
+      <c r="L35" s="172"/>
+      <c r="M35" s="173"/>
+      <c r="N35" s="174"/>
     </row>
     <row r="36" spans="2:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="70" t="s">
+      <c r="B36" s="183" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="71"/>
-      <c r="M36" s="71"/>
-      <c r="N36" s="72"/>
+      <c r="C36" s="184"/>
+      <c r="D36" s="184"/>
+      <c r="E36" s="184"/>
+      <c r="F36" s="184"/>
+      <c r="G36" s="184"/>
+      <c r="H36" s="184"/>
+      <c r="I36" s="184"/>
+      <c r="J36" s="184"/>
+      <c r="K36" s="184"/>
+      <c r="L36" s="184"/>
+      <c r="M36" s="184"/>
+      <c r="N36" s="185"/>
       <c r="S36" s="8"/>
     </row>
     <row r="37" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="129" t="s">
+      <c r="B37" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="130" t="s">
+      <c r="C37" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="130" t="s">
+      <c r="D37" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="E37" s="69" t="s">
+      <c r="E37" s="182" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
+      <c r="F37" s="182"/>
+      <c r="G37" s="182"/>
+      <c r="H37" s="182"/>
       <c r="I37" s="27" t="s">
         <v>73</v>
       </c>
       <c r="J37" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="K37" s="66" t="s">
+      <c r="K37" s="127" t="s">
         <v>15</v>
       </c>
-      <c r="L37" s="67"/>
-      <c r="M37" s="67"/>
-      <c r="N37" s="68"/>
+      <c r="L37" s="128"/>
+      <c r="M37" s="128"/>
+      <c r="N37" s="181"/>
       <c r="S37" s="8"/>
     </row>
     <row r="38" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="125">
+      <c r="C38" s="51">
         <v>46314</v>
       </c>
-      <c r="D38" s="127" t="s">
+      <c r="D38" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="128" t="s">
+      <c r="E38" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="128"/>
-      <c r="G38" s="128"/>
-      <c r="H38" s="128"/>
+      <c r="F38" s="180"/>
+      <c r="G38" s="180"/>
+      <c r="H38" s="180"/>
       <c r="I38" s="29">
         <v>0</v>
       </c>
       <c r="J38" s="29">
         <v>0</v>
       </c>
-      <c r="K38" s="58" t="s">
+      <c r="K38" s="177" t="s">
         <v>135</v>
       </c>
-      <c r="L38" s="59"/>
-      <c r="M38" s="59"/>
-      <c r="N38" s="60"/>
+      <c r="L38" s="178"/>
+      <c r="M38" s="178"/>
+      <c r="N38" s="179"/>
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
       <c r="Q38" s="19"/>
@@ -3944,30 +3941,30 @@
       <c r="B39" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="125">
+      <c r="C39" s="51">
         <v>46314</v>
       </c>
-      <c r="D39" s="127" t="s">
+      <c r="D39" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="128" t="s">
+      <c r="E39" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F39" s="128"/>
-      <c r="G39" s="128"/>
-      <c r="H39" s="128"/>
+      <c r="F39" s="180"/>
+      <c r="G39" s="180"/>
+      <c r="H39" s="180"/>
       <c r="I39" s="29">
         <v>0</v>
       </c>
       <c r="J39" s="29">
         <v>0</v>
       </c>
-      <c r="K39" s="58" t="s">
+      <c r="K39" s="177" t="s">
         <v>135</v>
       </c>
-      <c r="L39" s="59"/>
-      <c r="M39" s="59"/>
-      <c r="N39" s="60"/>
+      <c r="L39" s="178"/>
+      <c r="M39" s="178"/>
+      <c r="N39" s="179"/>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
       <c r="Q39" s="19"/>
@@ -3978,30 +3975,30 @@
       <c r="B40" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="125">
+      <c r="C40" s="51">
         <v>46314</v>
       </c>
-      <c r="D40" s="127" t="s">
+      <c r="D40" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="E40" s="128" t="s">
+      <c r="E40" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F40" s="128"/>
-      <c r="G40" s="128"/>
-      <c r="H40" s="128"/>
+      <c r="F40" s="180"/>
+      <c r="G40" s="180"/>
+      <c r="H40" s="180"/>
       <c r="I40" s="29">
         <v>0</v>
       </c>
       <c r="J40" s="29">
         <v>0</v>
       </c>
-      <c r="K40" s="58" t="s">
+      <c r="K40" s="177" t="s">
         <v>135</v>
       </c>
-      <c r="L40" s="59"/>
-      <c r="M40" s="59"/>
-      <c r="N40" s="60"/>
+      <c r="L40" s="178"/>
+      <c r="M40" s="178"/>
+      <c r="N40" s="179"/>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
       <c r="Q40" s="19"/>
@@ -4010,18 +4007,18 @@
     </row>
     <row r="41" spans="2:19" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="7"/>
-      <c r="C41" s="126"/>
-      <c r="D41" s="127"/>
-      <c r="E41" s="128"/>
-      <c r="F41" s="128"/>
-      <c r="G41" s="128"/>
-      <c r="H41" s="128"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="180"/>
+      <c r="F41" s="180"/>
+      <c r="G41" s="180"/>
+      <c r="H41" s="180"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="59"/>
-      <c r="M41" s="59"/>
-      <c r="N41" s="60"/>
+      <c r="K41" s="177"/>
+      <c r="L41" s="178"/>
+      <c r="M41" s="178"/>
+      <c r="N41" s="179"/>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
       <c r="Q41" s="19"/>
@@ -4029,21 +4026,21 @@
       <c r="S41" s="8"/>
     </row>
     <row r="42" spans="2:19" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="B42" s="122" t="s">
+      <c r="B42" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="123"/>
-      <c r="D42" s="123"/>
-      <c r="E42" s="123"/>
-      <c r="F42" s="123"/>
-      <c r="G42" s="123"/>
-      <c r="H42" s="123"/>
-      <c r="I42" s="124"/>
-      <c r="J42" s="131"/>
-      <c r="K42" s="123"/>
-      <c r="L42" s="123"/>
-      <c r="M42" s="123"/>
-      <c r="N42" s="132"/>
+      <c r="C42" s="94"/>
+      <c r="D42" s="94"/>
+      <c r="E42" s="94"/>
+      <c r="F42" s="94"/>
+      <c r="G42" s="94"/>
+      <c r="H42" s="94"/>
+      <c r="I42" s="95"/>
+      <c r="J42" s="96"/>
+      <c r="K42" s="94"/>
+      <c r="L42" s="94"/>
+      <c r="M42" s="94"/>
+      <c r="N42" s="97"/>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
       <c r="Q42" s="19"/>
@@ -4060,20 +4057,20 @@
       <c r="D43" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="E43" s="52" t="s">
+      <c r="E43" s="186" t="s">
         <v>6</v>
       </c>
-      <c r="F43" s="52"/>
-      <c r="G43" s="52"/>
-      <c r="H43" s="52"/>
+      <c r="F43" s="186"/>
+      <c r="G43" s="186"/>
+      <c r="H43" s="186"/>
       <c r="I43" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="J43" s="115"/>
-      <c r="K43" s="116"/>
-      <c r="L43" s="116"/>
-      <c r="M43" s="116"/>
-      <c r="N43" s="117"/>
+      <c r="J43" s="90"/>
+      <c r="K43" s="91"/>
+      <c r="L43" s="91"/>
+      <c r="M43" s="91"/>
+      <c r="N43" s="92"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="17"/>
@@ -4084,26 +4081,26 @@
       <c r="B44" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="125">
+      <c r="C44" s="51">
         <v>46314</v>
       </c>
-      <c r="D44" s="127" t="s">
+      <c r="D44" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="128" t="s">
+      <c r="E44" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F44" s="128"/>
-      <c r="G44" s="128"/>
-      <c r="H44" s="128"/>
+      <c r="F44" s="180"/>
+      <c r="G44" s="180"/>
+      <c r="H44" s="180"/>
       <c r="I44" s="29">
         <v>1137</v>
       </c>
-      <c r="J44" s="118"/>
-      <c r="K44" s="119"/>
-      <c r="L44" s="119"/>
-      <c r="M44" s="119"/>
-      <c r="N44" s="119"/>
+      <c r="J44" s="86"/>
+      <c r="K44" s="87"/>
+      <c r="L44" s="87"/>
+      <c r="M44" s="87"/>
+      <c r="N44" s="87"/>
       <c r="O44" s="48">
         <v>14003101001</v>
       </c>
@@ -4120,26 +4117,26 @@
       <c r="B45" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="125">
+      <c r="C45" s="51">
         <v>46314</v>
       </c>
-      <c r="D45" s="127" t="s">
+      <c r="D45" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="128" t="s">
+      <c r="E45" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F45" s="128"/>
-      <c r="G45" s="128"/>
-      <c r="H45" s="128"/>
+      <c r="F45" s="180"/>
+      <c r="G45" s="180"/>
+      <c r="H45" s="180"/>
       <c r="I45" s="29">
         <v>1417.5</v>
       </c>
-      <c r="J45" s="120"/>
-      <c r="K45" s="121"/>
-      <c r="L45" s="121"/>
-      <c r="M45" s="121"/>
-      <c r="N45" s="121"/>
+      <c r="J45" s="88"/>
+      <c r="K45" s="89"/>
+      <c r="L45" s="89"/>
+      <c r="M45" s="89"/>
+      <c r="N45" s="89"/>
       <c r="O45" s="7">
         <v>14003201001</v>
       </c>
@@ -4156,26 +4153,26 @@
       <c r="B46" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="125">
+      <c r="C46" s="51">
         <v>46314</v>
       </c>
-      <c r="D46" s="127" t="s">
+      <c r="D46" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="E46" s="128" t="s">
+      <c r="E46" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F46" s="128"/>
-      <c r="G46" s="128"/>
-      <c r="H46" s="128"/>
+      <c r="F46" s="180"/>
+      <c r="G46" s="180"/>
+      <c r="H46" s="180"/>
       <c r="I46" s="29">
         <v>454</v>
       </c>
-      <c r="J46" s="120"/>
-      <c r="K46" s="121"/>
-      <c r="L46" s="121"/>
-      <c r="M46" s="121"/>
-      <c r="N46" s="121"/>
+      <c r="J46" s="88"/>
+      <c r="K46" s="89"/>
+      <c r="L46" s="89"/>
+      <c r="M46" s="89"/>
+      <c r="N46" s="89"/>
       <c r="O46" s="7">
         <v>13978401001</v>
       </c>
@@ -4192,60 +4189,60 @@
       <c r="B47" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="125">
+      <c r="C47" s="51">
         <v>46314</v>
       </c>
-      <c r="D47" s="127" t="s">
+      <c r="D47" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="128" t="s">
+      <c r="E47" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="F47" s="128"/>
-      <c r="G47" s="128"/>
-      <c r="H47" s="128"/>
+      <c r="F47" s="180"/>
+      <c r="G47" s="180"/>
+      <c r="H47" s="180"/>
       <c r="I47" s="29">
         <v>1098</v>
       </c>
-      <c r="J47" s="120"/>
-      <c r="K47" s="121"/>
-      <c r="L47" s="121"/>
-      <c r="M47" s="121"/>
-      <c r="N47" s="121"/>
+      <c r="J47" s="88"/>
+      <c r="K47" s="89"/>
+      <c r="L47" s="89"/>
+      <c r="M47" s="89"/>
+      <c r="N47" s="89"/>
       <c r="O47" s="4"/>
     </row>
     <row r="48" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B48" s="7"/>
-      <c r="C48" s="125"/>
-      <c r="D48" s="127"/>
-      <c r="E48" s="128"/>
-      <c r="F48" s="128"/>
-      <c r="G48" s="128"/>
-      <c r="H48" s="128"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="180"/>
+      <c r="F48" s="180"/>
+      <c r="G48" s="180"/>
+      <c r="H48" s="180"/>
       <c r="I48" s="29"/>
-      <c r="J48" s="120"/>
-      <c r="K48" s="121"/>
-      <c r="L48" s="121"/>
-      <c r="M48" s="121"/>
-      <c r="N48" s="121"/>
+      <c r="J48" s="88"/>
+      <c r="K48" s="89"/>
+      <c r="L48" s="89"/>
+      <c r="M48" s="89"/>
+      <c r="N48" s="89"/>
       <c r="O48" s="4">
         <v>13851401001</v>
       </c>
     </row>
     <row r="49" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B49" s="125"/>
-      <c r="C49" s="126"/>
-      <c r="D49" s="127"/>
-      <c r="E49" s="92"/>
-      <c r="F49" s="92"/>
-      <c r="G49" s="92"/>
-      <c r="H49" s="92"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="117"/>
+      <c r="G49" s="117"/>
+      <c r="H49" s="117"/>
       <c r="I49" s="29"/>
-      <c r="J49" s="120"/>
-      <c r="K49" s="121"/>
-      <c r="L49" s="121"/>
-      <c r="M49" s="121"/>
-      <c r="N49" s="121"/>
+      <c r="J49" s="88"/>
+      <c r="K49" s="89"/>
+      <c r="L49" s="89"/>
+      <c r="M49" s="89"/>
+      <c r="N49" s="89"/>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.3"/>
     <row r="51" spans="2:14" x14ac:dyDescent="0.3"/>
@@ -4343,6 +4340,83 @@
     <row r="143" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K41:N41"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="B36:N36"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:J28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="B27:N27"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K26:M26"/>
     <mergeCell ref="E11:H11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="J44:N49"/>
@@ -4367,83 +4441,6 @@
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="N7:Q7"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="B27:N27"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:J28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="K37:N37"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="B36:N36"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K41:N41"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E38:H38"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="2">
@@ -7165,6 +7162,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="86c6d835-384d-4eee-b5e4-7a7d42cb3d19" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004A4A59D84FFE1748BB38BBBF60A87067" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="122dd576e940e33e9bdee9d882a1d0b8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="86c6d835-384d-4eee-b5e4-7a7d42cb3d19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ef1bdbddccf683fbaa0b0495f4025495" ns3:_="">
     <xsd:import namespace="86c6d835-384d-4eee-b5e4-7a7d42cb3d19"/>
@@ -7320,24 +7334,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54BB2CB7-F996-4C7B-B8F6-D759D6846113}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="86c6d835-384d-4eee-b5e4-7a7d42cb3d19"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="86c6d835-384d-4eee-b5e4-7a7d42cb3d19" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{601125AE-989D-4A8E-B764-68DA4A2ACCDA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A98C6C55-1841-4DCB-B412-B1F89DBD7BD9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7353,28 +7374,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{601125AE-989D-4A8E-B764-68DA4A2ACCDA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54BB2CB7-F996-4C7B-B8F6-D759D6846113}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="86c6d835-384d-4eee-b5e4-7a7d42cb3d19"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>